--- a/Avances de ejecución PDA 2026.xlsx
+++ b/Avances de ejecución PDA 2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Formación\Innovación\Proyectos\Tablero de control\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE625675-0165-4FE8-8C6F-827EE62D6C35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F22C601B-4DD8-4173-A8CA-9DF63330BC5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="736" xr2:uid="{937C6B1A-F6BF-4BC2-A9ED-700DD94C722F}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="428">
   <si>
     <t>PROCESO</t>
   </si>
@@ -1409,26 +1409,31 @@
     <t>Docentes formados y acompañados</t>
   </si>
   <si>
-    <t>Alcanzar 800 nuevos CI</t>
-  </si>
-  <si>
-    <t>Alcanzar 700 CI fortalecidos</t>
-  </si>
-  <si>
     <t>Actualización y mejora de los contenidos educativos digitales</t>
   </si>
   <si>
-    <t>Actividades para la familia con padres y cuidadores</t>
-  </si>
-  <si>
-    <t>Estudiantes formados y acompañados</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eventos y espacios de formación
-</t>
-  </si>
-  <si>
     <t>AVANCE DE EJECUCIÓN PLAN DE ACCIÓN 2026</t>
+  </si>
+  <si>
+    <t>Alcanzar 800 nuevos Centros de Interés - Línea 1</t>
+  </si>
+  <si>
+    <t>Alcanzar 700 Centros de Interés fortalecidos - Linea 2</t>
+  </si>
+  <si>
+    <t>Actividades para la familia</t>
+  </si>
+  <si>
+    <t>Estudiantes participantes en procesos de formación</t>
+  </si>
+  <si>
+    <t>Encuentros, eventos y espacios de participación y/o formación</t>
+  </si>
+  <si>
+    <t>Alcanzar  400 nuevas Iniciativas Escolares que integran la Tecnologia - Línea 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iniciativas Escolares </t>
   </si>
 </sst>
 </file>
@@ -1771,7 +1776,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="42">
+  <borders count="41">
     <border>
       <left/>
       <right/>
@@ -2281,19 +2286,6 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="8" tint="0.59996337778862885"/>
-      </left>
-      <right style="thin">
-        <color theme="8" tint="0.59996337778862885"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color theme="8" tint="0.59996337778862885"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF000000"/>
       </left>
       <right style="thin">
@@ -2328,7 +2320,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="201">
+  <cellXfs count="198">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2718,9 +2710,6 @@
     <xf numFmtId="3" fontId="20" fillId="21" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2748,15 +2737,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="30" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2769,7 +2749,7 @@
     <xf numFmtId="0" fontId="30" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2778,17 +2758,14 @@
     <xf numFmtId="1" fontId="30" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2805,12 +2782,12 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2876,6 +2853,12 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="9">
@@ -3318,327 +3301,336 @@
   <dimension ref="A1:U373"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="36" style="155" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="38" style="154" customWidth="1"/>
     <col min="2" max="2" width="9.140625" style="15" customWidth="1"/>
     <col min="3" max="3" width="13" style="15" customWidth="1"/>
     <col min="4" max="15" width="12.140625" style="21" customWidth="1"/>
     <col min="16" max="16384" width="9.140625" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="150" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="171" t="s">
+    <row r="1" spans="1:21" s="149" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="196" t="s">
+        <v>420</v>
+      </c>
+      <c r="C1" s="196"/>
+      <c r="D1" s="196"/>
+      <c r="E1" s="196"/>
+      <c r="F1" s="196"/>
+      <c r="G1" s="196"/>
+      <c r="H1" s="196"/>
+      <c r="I1" s="196"/>
+      <c r="J1" s="196"/>
+      <c r="K1" s="196"/>
+      <c r="L1" s="196"/>
+      <c r="M1" s="196"/>
+      <c r="N1" s="196"/>
+      <c r="O1" s="196"/>
+      <c r="P1" s="148"/>
+      <c r="Q1" s="148"/>
+      <c r="R1" s="148"/>
+      <c r="S1" s="148"/>
+      <c r="T1" s="148"/>
+      <c r="U1" s="148"/>
+    </row>
+    <row r="2" spans="1:21" s="147" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A2" s="167" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="167" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="167" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="168" t="s">
+        <v>404</v>
+      </c>
+      <c r="E2" s="168" t="s">
+        <v>405</v>
+      </c>
+      <c r="F2" s="168" t="s">
+        <v>406</v>
+      </c>
+      <c r="G2" s="168" t="s">
+        <v>407</v>
+      </c>
+      <c r="H2" s="168" t="s">
+        <v>408</v>
+      </c>
+      <c r="I2" s="168" t="s">
+        <v>409</v>
+      </c>
+      <c r="J2" s="168" t="s">
+        <v>410</v>
+      </c>
+      <c r="K2" s="168" t="s">
+        <v>411</v>
+      </c>
+      <c r="L2" s="168" t="s">
+        <v>412</v>
+      </c>
+      <c r="M2" s="168" t="s">
+        <v>413</v>
+      </c>
+      <c r="N2" s="168" t="s">
+        <v>414</v>
+      </c>
+      <c r="O2" s="168" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" s="156" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="159" t="s">
+        <v>416</v>
+      </c>
+      <c r="B3" s="163">
+        <v>4</v>
+      </c>
+      <c r="C3" s="157" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="169"/>
+      <c r="E3" s="169"/>
+      <c r="F3" s="169">
+        <v>1</v>
+      </c>
+      <c r="G3" s="169"/>
+      <c r="H3" s="169"/>
+      <c r="I3" s="169">
+        <v>1</v>
+      </c>
+      <c r="J3" s="169"/>
+      <c r="K3" s="169"/>
+      <c r="L3" s="169"/>
+      <c r="M3" s="169"/>
+      <c r="N3" s="169"/>
+      <c r="O3" s="169"/>
+    </row>
+    <row r="4" spans="1:21" s="156" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="159" t="s">
+        <v>417</v>
+      </c>
+      <c r="B4" s="163">
+        <v>5</v>
+      </c>
+      <c r="C4" s="157" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="169"/>
+      <c r="E4" s="169"/>
+      <c r="F4" s="169"/>
+      <c r="G4" s="169">
+        <v>2</v>
+      </c>
+      <c r="H4" s="169">
+        <v>1</v>
+      </c>
+      <c r="I4" s="169"/>
+      <c r="J4" s="169"/>
+      <c r="K4" s="169"/>
+      <c r="L4" s="169"/>
+      <c r="M4" s="169"/>
+      <c r="N4" s="169"/>
+      <c r="O4" s="169"/>
+    </row>
+    <row r="5" spans="1:21" s="156" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="159" t="s">
+        <v>418</v>
+      </c>
+      <c r="B5" s="163">
+        <v>3600</v>
+      </c>
+      <c r="C5" s="157" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="169"/>
+      <c r="E5" s="169"/>
+      <c r="F5" s="169"/>
+      <c r="G5" s="169"/>
+      <c r="H5" s="169"/>
+      <c r="I5" s="169"/>
+      <c r="J5" s="169"/>
+      <c r="K5" s="169"/>
+      <c r="L5" s="169"/>
+      <c r="M5" s="169"/>
+      <c r="N5" s="169"/>
+      <c r="O5" s="169"/>
+    </row>
+    <row r="6" spans="1:21" s="158" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="165" t="s">
+        <v>421</v>
+      </c>
+      <c r="B6" s="163">
+        <v>875</v>
+      </c>
+      <c r="C6" s="157" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="170"/>
+      <c r="E6" s="169">
+        <v>688</v>
+      </c>
+      <c r="F6" s="169">
+        <v>12</v>
+      </c>
+      <c r="G6" s="169"/>
+      <c r="H6" s="169"/>
+      <c r="I6" s="169"/>
+      <c r="J6" s="169"/>
+      <c r="K6" s="169"/>
+      <c r="L6" s="169"/>
+      <c r="M6" s="169"/>
+      <c r="N6" s="169"/>
+      <c r="O6" s="169"/>
+    </row>
+    <row r="7" spans="1:21" s="158" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="165" t="s">
+        <v>422</v>
+      </c>
+      <c r="B7" s="163">
+        <v>775</v>
+      </c>
+      <c r="C7" s="157" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="170"/>
+      <c r="E7" s="169">
+        <v>588</v>
+      </c>
+      <c r="F7" s="169">
+        <v>12</v>
+      </c>
+      <c r="G7" s="169"/>
+      <c r="H7" s="169"/>
+      <c r="I7" s="169"/>
+      <c r="J7" s="169"/>
+      <c r="K7" s="169"/>
+      <c r="L7" s="169"/>
+      <c r="M7" s="169"/>
+      <c r="N7" s="169"/>
+      <c r="O7" s="169"/>
+    </row>
+    <row r="8" spans="1:21" s="158" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="159" t="s">
+        <v>419</v>
+      </c>
+      <c r="B8" s="163">
+        <v>2</v>
+      </c>
+      <c r="C8" s="157" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="170"/>
+      <c r="E8" s="169"/>
+      <c r="F8" s="169"/>
+      <c r="G8" s="169"/>
+      <c r="H8" s="169"/>
+      <c r="I8" s="169"/>
+      <c r="J8" s="169"/>
+      <c r="K8" s="169"/>
+      <c r="L8" s="169"/>
+      <c r="M8" s="169"/>
+      <c r="N8" s="169"/>
+      <c r="O8" s="169"/>
+    </row>
+    <row r="9" spans="1:21" s="158" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="159" t="s">
+        <v>423</v>
+      </c>
+      <c r="B9" s="163">
+        <v>1300</v>
+      </c>
+      <c r="C9" s="160" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="171"/>
+      <c r="E9" s="172"/>
+      <c r="F9" s="172"/>
+      <c r="G9" s="172"/>
+      <c r="H9" s="172"/>
+      <c r="I9" s="172"/>
+      <c r="J9" s="172"/>
+      <c r="K9" s="172"/>
+      <c r="L9" s="172"/>
+      <c r="M9" s="172"/>
+      <c r="N9" s="172"/>
+      <c r="O9" s="172"/>
+    </row>
+    <row r="10" spans="1:21" s="158" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="159" t="s">
+        <v>424</v>
+      </c>
+      <c r="B10" s="163">
+        <v>15000</v>
+      </c>
+      <c r="C10" s="161" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="173"/>
+      <c r="E10" s="173"/>
+      <c r="F10" s="173"/>
+      <c r="G10" s="173"/>
+      <c r="H10" s="173"/>
+      <c r="I10" s="173"/>
+      <c r="J10" s="173"/>
+      <c r="K10" s="173"/>
+      <c r="L10" s="173"/>
+      <c r="M10" s="173"/>
+      <c r="N10" s="173"/>
+      <c r="O10" s="173"/>
+    </row>
+    <row r="11" spans="1:21" s="162" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="166" t="s">
         <v>425</v>
       </c>
-      <c r="B1" s="171"/>
-      <c r="C1" s="171"/>
-      <c r="D1" s="171"/>
-      <c r="E1" s="171"/>
-      <c r="F1" s="171"/>
-      <c r="G1" s="171"/>
-      <c r="H1" s="171"/>
-      <c r="I1" s="171"/>
-      <c r="J1" s="171"/>
-      <c r="K1" s="171"/>
-      <c r="L1" s="171"/>
-      <c r="M1" s="171"/>
-      <c r="N1" s="171"/>
-      <c r="O1" s="171"/>
-      <c r="P1" s="149"/>
-      <c r="Q1" s="149"/>
-      <c r="R1" s="149"/>
-      <c r="S1" s="149"/>
-      <c r="T1" s="149"/>
-      <c r="U1" s="149"/>
-    </row>
-    <row r="2" spans="1:21" s="148" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A2" s="172" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="172" t="s">
+      <c r="B11" s="163">
+        <v>40</v>
+      </c>
+      <c r="C11" s="164" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="173"/>
+      <c r="E11" s="173"/>
+      <c r="F11" s="173"/>
+      <c r="G11" s="173"/>
+      <c r="H11" s="173">
+        <v>7</v>
+      </c>
+      <c r="I11" s="173">
         <v>3</v>
       </c>
-      <c r="C2" s="172" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="173" t="s">
-        <v>404</v>
-      </c>
-      <c r="E2" s="173" t="s">
-        <v>405</v>
-      </c>
-      <c r="F2" s="173" t="s">
-        <v>406</v>
-      </c>
-      <c r="G2" s="173" t="s">
-        <v>407</v>
-      </c>
-      <c r="H2" s="173" t="s">
-        <v>408</v>
-      </c>
-      <c r="I2" s="173" t="s">
-        <v>409</v>
-      </c>
-      <c r="J2" s="173" t="s">
-        <v>410</v>
-      </c>
-      <c r="K2" s="173" t="s">
-        <v>411</v>
-      </c>
-      <c r="L2" s="173" t="s">
-        <v>412</v>
-      </c>
-      <c r="M2" s="173" t="s">
-        <v>413</v>
-      </c>
-      <c r="N2" s="173" t="s">
-        <v>414</v>
-      </c>
-      <c r="O2" s="173" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" s="157" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="163" t="s">
-        <v>416</v>
-      </c>
-      <c r="B3" s="167">
-        <v>4</v>
-      </c>
-      <c r="C3" s="161" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="174"/>
-      <c r="E3" s="174"/>
-      <c r="F3" s="174">
-        <v>1</v>
-      </c>
-      <c r="G3" s="174"/>
-      <c r="H3" s="174"/>
-      <c r="I3" s="174"/>
-      <c r="J3" s="174"/>
-      <c r="K3" s="174"/>
-      <c r="L3" s="174"/>
-      <c r="M3" s="174"/>
-      <c r="N3" s="174"/>
-      <c r="O3" s="174"/>
-    </row>
-    <row r="4" spans="1:21" s="157" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="163" t="s">
-        <v>417</v>
-      </c>
-      <c r="B4" s="167">
-        <v>5</v>
-      </c>
-      <c r="C4" s="161" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="174"/>
-      <c r="E4" s="174"/>
-      <c r="F4" s="174"/>
-      <c r="G4" s="174">
-        <v>2</v>
-      </c>
-      <c r="H4" s="174">
-        <v>1</v>
-      </c>
-      <c r="I4" s="174"/>
-      <c r="J4" s="174"/>
-      <c r="K4" s="174"/>
-      <c r="L4" s="174"/>
-      <c r="M4" s="174"/>
-      <c r="N4" s="174"/>
-      <c r="O4" s="174"/>
-    </row>
-    <row r="5" spans="1:21" s="157" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="163" t="s">
-        <v>418</v>
-      </c>
-      <c r="B5" s="167">
-        <v>3000</v>
-      </c>
-      <c r="C5" s="161" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="174"/>
-      <c r="E5" s="174"/>
-      <c r="F5" s="174"/>
-      <c r="G5" s="174"/>
-      <c r="H5" s="174"/>
-      <c r="I5" s="174"/>
-      <c r="J5" s="174"/>
-      <c r="K5" s="174"/>
-      <c r="L5" s="174"/>
-      <c r="M5" s="174"/>
-      <c r="N5" s="174"/>
-      <c r="O5" s="174"/>
-    </row>
-    <row r="6" spans="1:21" s="162" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="169" t="s">
-        <v>419</v>
-      </c>
-      <c r="B6" s="167">
-        <v>800</v>
-      </c>
-      <c r="C6" s="161" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="175"/>
-      <c r="E6" s="174">
-        <v>688</v>
-      </c>
-      <c r="F6" s="174">
-        <v>12</v>
-      </c>
-      <c r="G6" s="174"/>
-      <c r="H6" s="174"/>
-      <c r="I6" s="174"/>
-      <c r="J6" s="174"/>
-      <c r="K6" s="174"/>
-      <c r="L6" s="174"/>
-      <c r="M6" s="174"/>
-      <c r="N6" s="174"/>
-      <c r="O6" s="174"/>
-    </row>
-    <row r="7" spans="1:21" s="162" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="169" t="s">
-        <v>420</v>
-      </c>
-      <c r="B7" s="167">
-        <v>700</v>
-      </c>
-      <c r="C7" s="161" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="175"/>
-      <c r="E7" s="174">
-        <v>588</v>
-      </c>
-      <c r="F7" s="174">
-        <v>12</v>
-      </c>
-      <c r="G7" s="174"/>
-      <c r="H7" s="174"/>
-      <c r="I7" s="174"/>
-      <c r="J7" s="174"/>
-      <c r="K7" s="174"/>
-      <c r="L7" s="174"/>
-      <c r="M7" s="174"/>
-      <c r="N7" s="174"/>
-      <c r="O7" s="174"/>
-    </row>
-    <row r="8" spans="1:21" s="162" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="163" t="s">
-        <v>421</v>
-      </c>
-      <c r="B8" s="167">
-        <v>2</v>
-      </c>
-      <c r="C8" s="161" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="175"/>
-      <c r="E8" s="174"/>
-      <c r="F8" s="174"/>
-      <c r="G8" s="174"/>
-      <c r="H8" s="174"/>
-      <c r="I8" s="174"/>
-      <c r="J8" s="174"/>
-      <c r="K8" s="174"/>
-      <c r="L8" s="174"/>
-      <c r="M8" s="174"/>
-      <c r="N8" s="174"/>
-      <c r="O8" s="174"/>
-    </row>
-    <row r="9" spans="1:21" s="162" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="163" t="s">
-        <v>422</v>
-      </c>
-      <c r="B9" s="167">
-        <v>1300</v>
-      </c>
-      <c r="C9" s="164" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" s="176"/>
-      <c r="E9" s="177"/>
-      <c r="F9" s="177"/>
-      <c r="G9" s="177"/>
-      <c r="H9" s="177"/>
-      <c r="I9" s="177"/>
-      <c r="J9" s="177"/>
-      <c r="K9" s="177"/>
-      <c r="L9" s="177"/>
-      <c r="M9" s="177"/>
-      <c r="N9" s="177"/>
-      <c r="O9" s="177"/>
-    </row>
-    <row r="10" spans="1:21" s="162" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="163" t="s">
-        <v>423</v>
-      </c>
-      <c r="B10" s="167">
-        <v>10000</v>
-      </c>
-      <c r="C10" s="165" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" s="178"/>
-      <c r="E10" s="178"/>
-      <c r="F10" s="178"/>
-      <c r="G10" s="178"/>
-      <c r="H10" s="178"/>
-      <c r="I10" s="178"/>
-      <c r="J10" s="178"/>
-      <c r="K10" s="178"/>
-      <c r="L10" s="178"/>
-      <c r="M10" s="178"/>
-      <c r="N10" s="178"/>
-      <c r="O10" s="178"/>
-    </row>
-    <row r="11" spans="1:21" s="166" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="170" t="s">
-        <v>424</v>
-      </c>
-      <c r="B11" s="167">
-        <v>25</v>
-      </c>
-      <c r="C11" s="168" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="178"/>
-      <c r="E11" s="178"/>
-      <c r="F11" s="178"/>
-      <c r="G11" s="178"/>
-      <c r="H11" s="178">
-        <v>7</v>
-      </c>
-      <c r="I11" s="178"/>
-      <c r="J11" s="178"/>
-      <c r="K11" s="178"/>
-      <c r="L11" s="178"/>
-      <c r="M11" s="178"/>
-      <c r="N11" s="178"/>
-      <c r="O11" s="178"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A12" s="159"/>
-      <c r="B12" s="158"/>
-      <c r="C12" s="160"/>
-      <c r="D12" s="147"/>
-      <c r="E12" s="147"/>
-      <c r="F12" s="147"/>
-      <c r="G12" s="147"/>
-      <c r="H12" s="147"/>
-      <c r="I12" s="147"/>
-      <c r="J12" s="147"/>
-      <c r="K12" s="147"/>
-      <c r="L12" s="147"/>
-      <c r="M12" s="147"/>
-      <c r="N12" s="147"/>
-      <c r="O12" s="147"/>
+      <c r="J11" s="173"/>
+      <c r="K11" s="173"/>
+      <c r="L11" s="173"/>
+      <c r="M11" s="173"/>
+      <c r="N11" s="173"/>
+      <c r="O11" s="173"/>
+    </row>
+    <row r="12" spans="1:21" ht="27" x14ac:dyDescent="0.3">
+      <c r="A12" s="166" t="s">
+        <v>426</v>
+      </c>
+      <c r="B12" s="163">
+        <v>400</v>
+      </c>
+      <c r="C12" s="197" t="s">
+        <v>427</v>
+      </c>
+      <c r="D12" s="173"/>
+      <c r="E12" s="173"/>
+      <c r="F12" s="173"/>
+      <c r="G12" s="173"/>
+      <c r="H12" s="173"/>
+      <c r="I12" s="173"/>
+      <c r="J12" s="173"/>
+      <c r="K12" s="173"/>
+      <c r="L12" s="173"/>
+      <c r="M12" s="173"/>
+      <c r="N12" s="173"/>
+      <c r="O12" s="173"/>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A13" s="156"/>
+      <c r="A13" s="155"/>
       <c r="B13" s="18"/>
       <c r="C13" s="19"/>
       <c r="D13" s="20"/>
@@ -3655,7 +3647,7 @@
       <c r="O13" s="20"/>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A14" s="156"/>
+      <c r="A14" s="155"/>
       <c r="B14" s="18"/>
       <c r="C14" s="19"/>
       <c r="D14" s="20"/>
@@ -3672,7 +3664,7 @@
       <c r="O14" s="20"/>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A15" s="156"/>
+      <c r="A15" s="155"/>
       <c r="B15" s="18"/>
       <c r="C15" s="19"/>
       <c r="D15" s="20"/>
@@ -3689,7 +3681,7 @@
       <c r="O15" s="20"/>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A16" s="156"/>
+      <c r="A16" s="155"/>
       <c r="B16" s="18"/>
       <c r="C16" s="19"/>
       <c r="D16" s="20"/>
@@ -3706,7 +3698,7 @@
       <c r="O16" s="20"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A17" s="156"/>
+      <c r="A17" s="155"/>
       <c r="B17" s="18"/>
       <c r="C17" s="19"/>
       <c r="D17" s="20"/>
@@ -3723,7 +3715,7 @@
       <c r="O17" s="20"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A18" s="156"/>
+      <c r="A18" s="155"/>
       <c r="B18" s="18"/>
       <c r="C18" s="19"/>
       <c r="D18" s="20"/>
@@ -3740,7 +3732,7 @@
       <c r="O18" s="20"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A19" s="156"/>
+      <c r="A19" s="155"/>
       <c r="B19" s="18"/>
       <c r="C19" s="19"/>
       <c r="D19" s="20"/>
@@ -3757,7 +3749,7 @@
       <c r="O19" s="20"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A20" s="156"/>
+      <c r="A20" s="155"/>
       <c r="B20" s="18"/>
       <c r="C20" s="19"/>
       <c r="D20" s="20"/>
@@ -3774,7 +3766,7 @@
       <c r="O20" s="20"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A21" s="156"/>
+      <c r="A21" s="155"/>
       <c r="B21" s="18"/>
       <c r="C21" s="19"/>
       <c r="D21" s="20"/>
@@ -3791,7 +3783,7 @@
       <c r="O21" s="20"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A22" s="156"/>
+      <c r="A22" s="155"/>
       <c r="B22" s="18"/>
       <c r="C22" s="19"/>
       <c r="D22" s="20"/>
@@ -3808,7 +3800,7 @@
       <c r="O22" s="20"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A23" s="156"/>
+      <c r="A23" s="155"/>
       <c r="B23" s="18"/>
       <c r="C23" s="19"/>
       <c r="D23" s="20"/>
@@ -3825,7 +3817,7 @@
       <c r="O23" s="20"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A24" s="156"/>
+      <c r="A24" s="155"/>
       <c r="B24" s="18"/>
       <c r="C24" s="19"/>
       <c r="D24" s="20"/>
@@ -3842,7 +3834,7 @@
       <c r="O24" s="20"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A25" s="156"/>
+      <c r="A25" s="155"/>
       <c r="B25" s="18"/>
       <c r="C25" s="19"/>
       <c r="D25" s="20"/>
@@ -3859,7 +3851,7 @@
       <c r="O25" s="20"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A26" s="156"/>
+      <c r="A26" s="155"/>
       <c r="B26" s="18"/>
       <c r="C26" s="19"/>
       <c r="D26" s="20"/>
@@ -3876,7 +3868,7 @@
       <c r="O26" s="20"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A27" s="156"/>
+      <c r="A27" s="155"/>
       <c r="B27" s="18"/>
       <c r="C27" s="19"/>
       <c r="D27" s="20"/>
@@ -3893,7 +3885,7 @@
       <c r="O27" s="20"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A28" s="156"/>
+      <c r="A28" s="155"/>
       <c r="B28" s="18"/>
       <c r="C28" s="19"/>
       <c r="D28" s="20"/>
@@ -3910,7 +3902,7 @@
       <c r="O28" s="20"/>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A29" s="156"/>
+      <c r="A29" s="155"/>
       <c r="B29" s="18"/>
       <c r="C29" s="19"/>
       <c r="D29" s="20"/>
@@ -3927,7 +3919,7 @@
       <c r="O29" s="20"/>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A30" s="156"/>
+      <c r="A30" s="155"/>
       <c r="B30" s="18"/>
       <c r="C30" s="19"/>
       <c r="D30" s="20"/>
@@ -3944,7 +3936,7 @@
       <c r="O30" s="20"/>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A31" s="156"/>
+      <c r="A31" s="155"/>
       <c r="B31" s="18"/>
       <c r="C31" s="19"/>
       <c r="D31" s="20"/>
@@ -3961,7 +3953,7 @@
       <c r="O31" s="20"/>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A32" s="156"/>
+      <c r="A32" s="155"/>
       <c r="B32" s="18"/>
       <c r="C32" s="19"/>
       <c r="D32" s="20"/>
@@ -3978,7 +3970,7 @@
       <c r="O32" s="20"/>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A33" s="156"/>
+      <c r="A33" s="155"/>
       <c r="B33" s="18"/>
       <c r="C33" s="19"/>
       <c r="D33" s="20"/>
@@ -3995,7 +3987,7 @@
       <c r="O33" s="20"/>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A34" s="156"/>
+      <c r="A34" s="155"/>
       <c r="B34" s="18"/>
       <c r="C34" s="19"/>
       <c r="D34" s="20"/>
@@ -4012,7 +4004,7 @@
       <c r="O34" s="20"/>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A35" s="156"/>
+      <c r="A35" s="155"/>
       <c r="B35" s="18"/>
       <c r="C35" s="19"/>
       <c r="D35" s="20"/>
@@ -4029,7 +4021,7 @@
       <c r="O35" s="20"/>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A36" s="156"/>
+      <c r="A36" s="155"/>
       <c r="B36" s="18"/>
       <c r="C36" s="19"/>
       <c r="D36" s="20"/>
@@ -4046,7 +4038,7 @@
       <c r="O36" s="20"/>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A37" s="156"/>
+      <c r="A37" s="155"/>
       <c r="B37" s="18"/>
       <c r="C37" s="19"/>
       <c r="D37" s="20"/>
@@ -4063,7 +4055,7 @@
       <c r="O37" s="20"/>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A38" s="156"/>
+      <c r="A38" s="155"/>
       <c r="B38" s="18"/>
       <c r="C38" s="19"/>
       <c r="D38" s="20"/>
@@ -4080,7 +4072,7 @@
       <c r="O38" s="20"/>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A39" s="156"/>
+      <c r="A39" s="155"/>
       <c r="B39" s="18"/>
       <c r="C39" s="19"/>
       <c r="D39" s="20"/>
@@ -4097,7 +4089,7 @@
       <c r="O39" s="20"/>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A40" s="156"/>
+      <c r="A40" s="155"/>
       <c r="B40" s="18"/>
       <c r="C40" s="19"/>
       <c r="D40" s="20"/>
@@ -4114,7 +4106,7 @@
       <c r="O40" s="20"/>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A41" s="156"/>
+      <c r="A41" s="155"/>
       <c r="B41" s="18"/>
       <c r="C41" s="19"/>
       <c r="D41" s="20"/>
@@ -4131,7 +4123,7 @@
       <c r="O41" s="20"/>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A42" s="156"/>
+      <c r="A42" s="155"/>
       <c r="B42" s="18"/>
       <c r="C42" s="19"/>
       <c r="D42" s="20"/>
@@ -4148,7 +4140,7 @@
       <c r="O42" s="20"/>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A43" s="156"/>
+      <c r="A43" s="155"/>
       <c r="B43" s="18"/>
       <c r="C43" s="19"/>
       <c r="D43" s="20"/>
@@ -4165,7 +4157,7 @@
       <c r="O43" s="20"/>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A44" s="156"/>
+      <c r="A44" s="155"/>
       <c r="B44" s="18"/>
       <c r="C44" s="19"/>
       <c r="D44" s="20"/>
@@ -4182,7 +4174,7 @@
       <c r="O44" s="20"/>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A45" s="156"/>
+      <c r="A45" s="155"/>
       <c r="B45" s="18"/>
       <c r="C45" s="19"/>
       <c r="D45" s="20"/>
@@ -4199,7 +4191,7 @@
       <c r="O45" s="20"/>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A46" s="156"/>
+      <c r="A46" s="155"/>
       <c r="B46" s="18"/>
       <c r="C46" s="19"/>
       <c r="D46" s="20"/>
@@ -4216,7 +4208,7 @@
       <c r="O46" s="20"/>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A47" s="156"/>
+      <c r="A47" s="155"/>
       <c r="B47" s="18"/>
       <c r="C47" s="19"/>
       <c r="D47" s="20"/>
@@ -4233,7 +4225,7 @@
       <c r="O47" s="20"/>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A48" s="156"/>
+      <c r="A48" s="155"/>
       <c r="B48" s="18"/>
       <c r="C48" s="19"/>
       <c r="D48" s="20"/>
@@ -4250,7 +4242,7 @@
       <c r="O48" s="20"/>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A49" s="156"/>
+      <c r="A49" s="155"/>
       <c r="B49" s="18"/>
       <c r="C49" s="19"/>
       <c r="D49" s="20"/>
@@ -4267,7 +4259,7 @@
       <c r="O49" s="20"/>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A50" s="156"/>
+      <c r="A50" s="155"/>
       <c r="B50" s="18"/>
       <c r="C50" s="19"/>
       <c r="D50" s="20"/>
@@ -4284,7 +4276,7 @@
       <c r="O50" s="20"/>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A51" s="156"/>
+      <c r="A51" s="155"/>
       <c r="B51" s="18"/>
       <c r="C51" s="19"/>
       <c r="D51" s="20"/>
@@ -4301,7 +4293,7 @@
       <c r="O51" s="20"/>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A52" s="156"/>
+      <c r="A52" s="155"/>
       <c r="B52" s="18"/>
       <c r="C52" s="19"/>
       <c r="D52" s="20"/>
@@ -4318,7 +4310,7 @@
       <c r="O52" s="20"/>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A53" s="156"/>
+      <c r="A53" s="155"/>
       <c r="B53" s="18"/>
       <c r="C53" s="19"/>
       <c r="D53" s="20"/>
@@ -4335,7 +4327,7 @@
       <c r="O53" s="20"/>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A54" s="156"/>
+      <c r="A54" s="155"/>
       <c r="B54" s="18"/>
       <c r="C54" s="19"/>
       <c r="D54" s="20"/>
@@ -4352,7 +4344,7 @@
       <c r="O54" s="20"/>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A55" s="156"/>
+      <c r="A55" s="155"/>
       <c r="B55" s="18"/>
       <c r="C55" s="19"/>
       <c r="D55" s="20"/>
@@ -4369,7 +4361,7 @@
       <c r="O55" s="20"/>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A56" s="156"/>
+      <c r="A56" s="155"/>
       <c r="B56" s="18"/>
       <c r="C56" s="19"/>
       <c r="D56" s="20"/>
@@ -4386,7 +4378,7 @@
       <c r="O56" s="20"/>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A57" s="156"/>
+      <c r="A57" s="155"/>
       <c r="B57" s="18"/>
       <c r="C57" s="19"/>
       <c r="D57" s="20"/>
@@ -4403,7 +4395,7 @@
       <c r="O57" s="20"/>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A58" s="156"/>
+      <c r="A58" s="155"/>
       <c r="B58" s="18"/>
       <c r="C58" s="19"/>
       <c r="D58" s="20"/>
@@ -4420,7 +4412,7 @@
       <c r="O58" s="20"/>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A59" s="156"/>
+      <c r="A59" s="155"/>
       <c r="B59" s="18"/>
       <c r="C59" s="19"/>
       <c r="D59" s="20"/>
@@ -4437,7 +4429,7 @@
       <c r="O59" s="20"/>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A60" s="156"/>
+      <c r="A60" s="155"/>
       <c r="B60" s="18"/>
       <c r="C60" s="19"/>
       <c r="D60" s="20"/>
@@ -4454,7 +4446,7 @@
       <c r="O60" s="20"/>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A61" s="156"/>
+      <c r="A61" s="155"/>
       <c r="B61" s="18"/>
       <c r="C61" s="19"/>
       <c r="D61" s="20"/>
@@ -4471,7 +4463,7 @@
       <c r="O61" s="20"/>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A62" s="156"/>
+      <c r="A62" s="155"/>
       <c r="B62" s="18"/>
       <c r="C62" s="19"/>
       <c r="D62" s="20"/>
@@ -4488,7 +4480,7 @@
       <c r="O62" s="20"/>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A63" s="156"/>
+      <c r="A63" s="155"/>
       <c r="B63" s="18"/>
       <c r="C63" s="19"/>
       <c r="D63" s="20"/>
@@ -4505,7 +4497,7 @@
       <c r="O63" s="20"/>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A64" s="156"/>
+      <c r="A64" s="155"/>
       <c r="B64" s="18"/>
       <c r="C64" s="19"/>
       <c r="D64" s="20"/>
@@ -4522,7 +4514,7 @@
       <c r="O64" s="20"/>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A65" s="156"/>
+      <c r="A65" s="155"/>
       <c r="B65" s="18"/>
       <c r="C65" s="19"/>
       <c r="D65" s="20"/>
@@ -4539,7 +4531,7 @@
       <c r="O65" s="20"/>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A66" s="156"/>
+      <c r="A66" s="155"/>
       <c r="B66" s="18"/>
       <c r="C66" s="19"/>
       <c r="D66" s="20"/>
@@ -4556,7 +4548,7 @@
       <c r="O66" s="20"/>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A67" s="156"/>
+      <c r="A67" s="155"/>
       <c r="B67" s="18"/>
       <c r="C67" s="19"/>
       <c r="D67" s="20"/>
@@ -4573,7 +4565,7 @@
       <c r="O67" s="20"/>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A68" s="156"/>
+      <c r="A68" s="155"/>
       <c r="B68" s="18"/>
       <c r="C68" s="19"/>
       <c r="D68" s="20"/>
@@ -4590,7 +4582,7 @@
       <c r="O68" s="20"/>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A69" s="156"/>
+      <c r="A69" s="155"/>
       <c r="B69" s="18"/>
       <c r="C69" s="19"/>
       <c r="D69" s="20"/>
@@ -4607,7 +4599,7 @@
       <c r="O69" s="20"/>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A70" s="156"/>
+      <c r="A70" s="155"/>
       <c r="B70" s="18"/>
       <c r="C70" s="19"/>
       <c r="D70" s="20"/>
@@ -4624,7 +4616,7 @@
       <c r="O70" s="20"/>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A71" s="156"/>
+      <c r="A71" s="155"/>
       <c r="B71" s="18"/>
       <c r="C71" s="19"/>
       <c r="D71" s="20"/>
@@ -4641,7 +4633,7 @@
       <c r="O71" s="20"/>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A72" s="156"/>
+      <c r="A72" s="155"/>
       <c r="B72" s="18"/>
       <c r="C72" s="19"/>
       <c r="D72" s="20"/>
@@ -4658,7 +4650,7 @@
       <c r="O72" s="20"/>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A73" s="156"/>
+      <c r="A73" s="155"/>
       <c r="B73" s="18"/>
       <c r="C73" s="19"/>
       <c r="D73" s="20"/>
@@ -4675,7 +4667,7 @@
       <c r="O73" s="20"/>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A74" s="156"/>
+      <c r="A74" s="155"/>
       <c r="B74" s="18"/>
       <c r="C74" s="19"/>
       <c r="D74" s="20"/>
@@ -4692,7 +4684,7 @@
       <c r="O74" s="20"/>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A75" s="156"/>
+      <c r="A75" s="155"/>
       <c r="B75" s="18"/>
       <c r="C75" s="19"/>
       <c r="D75" s="20"/>
@@ -4709,7 +4701,7 @@
       <c r="O75" s="20"/>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A76" s="156"/>
+      <c r="A76" s="155"/>
       <c r="B76" s="18"/>
       <c r="C76" s="19"/>
       <c r="D76" s="20"/>
@@ -4726,7 +4718,7 @@
       <c r="O76" s="20"/>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A77" s="156"/>
+      <c r="A77" s="155"/>
       <c r="B77" s="18"/>
       <c r="C77" s="19"/>
       <c r="D77" s="20"/>
@@ -4743,7 +4735,7 @@
       <c r="O77" s="20"/>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A78" s="156"/>
+      <c r="A78" s="155"/>
       <c r="B78" s="18"/>
       <c r="C78" s="19"/>
       <c r="D78" s="20"/>
@@ -4760,7 +4752,7 @@
       <c r="O78" s="20"/>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A79" s="156"/>
+      <c r="A79" s="155"/>
       <c r="B79" s="18"/>
       <c r="C79" s="19"/>
       <c r="D79" s="20"/>
@@ -4777,7 +4769,7 @@
       <c r="O79" s="20"/>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A80" s="156"/>
+      <c r="A80" s="155"/>
       <c r="B80" s="18"/>
       <c r="C80" s="19"/>
       <c r="D80" s="20"/>
@@ -4794,7 +4786,7 @@
       <c r="O80" s="20"/>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A81" s="156"/>
+      <c r="A81" s="155"/>
       <c r="B81" s="18"/>
       <c r="C81" s="19"/>
       <c r="D81" s="20"/>
@@ -4811,7 +4803,7 @@
       <c r="O81" s="20"/>
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A82" s="156"/>
+      <c r="A82" s="155"/>
       <c r="B82" s="18"/>
       <c r="C82" s="19"/>
       <c r="D82" s="20"/>
@@ -4828,7 +4820,7 @@
       <c r="O82" s="20"/>
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A83" s="156"/>
+      <c r="A83" s="155"/>
       <c r="B83" s="18"/>
       <c r="C83" s="19"/>
       <c r="D83" s="20"/>
@@ -4845,7 +4837,7 @@
       <c r="O83" s="20"/>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A84" s="156"/>
+      <c r="A84" s="155"/>
       <c r="B84" s="18"/>
       <c r="C84" s="19"/>
       <c r="D84" s="20"/>
@@ -4862,7 +4854,7 @@
       <c r="O84" s="20"/>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A85" s="156"/>
+      <c r="A85" s="155"/>
       <c r="B85" s="18"/>
       <c r="C85" s="19"/>
       <c r="D85" s="20"/>
@@ -4879,7 +4871,7 @@
       <c r="O85" s="20"/>
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A86" s="156"/>
+      <c r="A86" s="155"/>
       <c r="B86" s="18"/>
       <c r="C86" s="19"/>
       <c r="D86" s="20"/>
@@ -4896,7 +4888,7 @@
       <c r="O86" s="20"/>
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A87" s="156"/>
+      <c r="A87" s="155"/>
       <c r="B87" s="18"/>
       <c r="C87" s="19"/>
       <c r="D87" s="20"/>
@@ -4913,7 +4905,7 @@
       <c r="O87" s="20"/>
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A88" s="156"/>
+      <c r="A88" s="155"/>
       <c r="B88" s="18"/>
       <c r="C88" s="19"/>
       <c r="D88" s="20"/>
@@ -4930,7 +4922,7 @@
       <c r="O88" s="20"/>
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A89" s="156"/>
+      <c r="A89" s="155"/>
       <c r="B89" s="18"/>
       <c r="C89" s="19"/>
       <c r="D89" s="20"/>
@@ -4947,7 +4939,7 @@
       <c r="O89" s="20"/>
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A90" s="156"/>
+      <c r="A90" s="155"/>
       <c r="B90" s="18"/>
       <c r="C90" s="19"/>
       <c r="D90" s="20"/>
@@ -4964,7 +4956,7 @@
       <c r="O90" s="20"/>
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A91" s="156"/>
+      <c r="A91" s="155"/>
       <c r="B91" s="18"/>
       <c r="C91" s="19"/>
       <c r="D91" s="20"/>
@@ -4981,7 +4973,7 @@
       <c r="O91" s="20"/>
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A92" s="156"/>
+      <c r="A92" s="155"/>
       <c r="B92" s="18"/>
       <c r="C92" s="19"/>
       <c r="D92" s="20"/>
@@ -4998,7 +4990,7 @@
       <c r="O92" s="20"/>
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A93" s="156"/>
+      <c r="A93" s="155"/>
       <c r="B93" s="18"/>
       <c r="C93" s="19"/>
       <c r="D93" s="20"/>
@@ -5015,7 +5007,7 @@
       <c r="O93" s="20"/>
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A94" s="156"/>
+      <c r="A94" s="155"/>
       <c r="B94" s="18"/>
       <c r="C94" s="19"/>
       <c r="D94" s="20"/>
@@ -5032,7 +5024,7 @@
       <c r="O94" s="20"/>
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A95" s="156"/>
+      <c r="A95" s="155"/>
       <c r="B95" s="18"/>
       <c r="C95" s="19"/>
       <c r="D95" s="20"/>
@@ -5049,7 +5041,7 @@
       <c r="O95" s="20"/>
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A96" s="156"/>
+      <c r="A96" s="155"/>
       <c r="B96" s="18"/>
       <c r="C96" s="19"/>
       <c r="D96" s="20"/>
@@ -5066,7 +5058,7 @@
       <c r="O96" s="20"/>
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A97" s="156"/>
+      <c r="A97" s="155"/>
       <c r="B97" s="18"/>
       <c r="C97" s="19"/>
       <c r="D97" s="20"/>
@@ -5083,7 +5075,7 @@
       <c r="O97" s="20"/>
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A98" s="156"/>
+      <c r="A98" s="155"/>
       <c r="B98" s="18"/>
       <c r="C98" s="19"/>
       <c r="D98" s="20"/>
@@ -5100,7 +5092,7 @@
       <c r="O98" s="20"/>
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A99" s="156"/>
+      <c r="A99" s="155"/>
       <c r="B99" s="18"/>
       <c r="C99" s="19"/>
       <c r="D99" s="20"/>
@@ -5117,7 +5109,7 @@
       <c r="O99" s="20"/>
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A100" s="156"/>
+      <c r="A100" s="155"/>
       <c r="B100" s="18"/>
       <c r="C100" s="19"/>
       <c r="D100" s="20"/>
@@ -5134,7 +5126,7 @@
       <c r="O100" s="20"/>
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A101" s="156"/>
+      <c r="A101" s="155"/>
       <c r="B101" s="18"/>
       <c r="C101" s="19"/>
       <c r="D101" s="20"/>
@@ -5151,7 +5143,7 @@
       <c r="O101" s="20"/>
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A102" s="156"/>
+      <c r="A102" s="155"/>
       <c r="B102" s="18"/>
       <c r="C102" s="19"/>
       <c r="D102" s="20"/>
@@ -5168,7 +5160,7 @@
       <c r="O102" s="20"/>
     </row>
     <row r="103" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A103" s="156"/>
+      <c r="A103" s="155"/>
       <c r="B103" s="18"/>
       <c r="C103" s="19"/>
       <c r="D103" s="20"/>
@@ -5185,7 +5177,7 @@
       <c r="O103" s="20"/>
     </row>
     <row r="104" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A104" s="156"/>
+      <c r="A104" s="155"/>
       <c r="B104" s="18"/>
       <c r="C104" s="19"/>
       <c r="D104" s="20"/>
@@ -5202,7 +5194,7 @@
       <c r="O104" s="20"/>
     </row>
     <row r="105" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A105" s="156"/>
+      <c r="A105" s="155"/>
       <c r="B105" s="18"/>
       <c r="C105" s="19"/>
       <c r="D105" s="20"/>
@@ -5219,7 +5211,7 @@
       <c r="O105" s="20"/>
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A106" s="156"/>
+      <c r="A106" s="155"/>
       <c r="B106" s="18"/>
       <c r="C106" s="19"/>
       <c r="D106" s="20"/>
@@ -5236,7 +5228,7 @@
       <c r="O106" s="20"/>
     </row>
     <row r="107" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A107" s="156"/>
+      <c r="A107" s="155"/>
       <c r="B107" s="18"/>
       <c r="C107" s="19"/>
       <c r="D107" s="20"/>
@@ -5253,7 +5245,7 @@
       <c r="O107" s="20"/>
     </row>
     <row r="108" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A108" s="156"/>
+      <c r="A108" s="155"/>
       <c r="B108" s="18"/>
       <c r="C108" s="19"/>
       <c r="D108" s="20"/>
@@ -5270,7 +5262,7 @@
       <c r="O108" s="20"/>
     </row>
     <row r="109" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A109" s="156"/>
+      <c r="A109" s="155"/>
       <c r="B109" s="18"/>
       <c r="C109" s="19"/>
       <c r="D109" s="20"/>
@@ -5287,7 +5279,7 @@
       <c r="O109" s="20"/>
     </row>
     <row r="110" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A110" s="156"/>
+      <c r="A110" s="155"/>
       <c r="B110" s="18"/>
       <c r="C110" s="19"/>
       <c r="D110" s="20"/>
@@ -5304,7 +5296,7 @@
       <c r="O110" s="20"/>
     </row>
     <row r="111" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A111" s="156"/>
+      <c r="A111" s="155"/>
       <c r="B111" s="18"/>
       <c r="C111" s="19"/>
       <c r="D111" s="20"/>
@@ -5321,7 +5313,7 @@
       <c r="O111" s="20"/>
     </row>
     <row r="112" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A112" s="156"/>
+      <c r="A112" s="155"/>
       <c r="B112" s="18"/>
       <c r="C112" s="19"/>
       <c r="D112" s="20"/>
@@ -5338,7 +5330,7 @@
       <c r="O112" s="20"/>
     </row>
     <row r="113" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A113" s="156"/>
+      <c r="A113" s="155"/>
       <c r="B113" s="18"/>
       <c r="C113" s="19"/>
       <c r="D113" s="20"/>
@@ -5355,7 +5347,7 @@
       <c r="O113" s="20"/>
     </row>
     <row r="114" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A114" s="156"/>
+      <c r="A114" s="155"/>
       <c r="B114" s="18"/>
       <c r="C114" s="19"/>
       <c r="D114" s="20"/>
@@ -5372,7 +5364,7 @@
       <c r="O114" s="20"/>
     </row>
     <row r="115" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A115" s="156"/>
+      <c r="A115" s="155"/>
       <c r="B115" s="18"/>
       <c r="C115" s="19"/>
       <c r="D115" s="20"/>
@@ -5389,7 +5381,7 @@
       <c r="O115" s="20"/>
     </row>
     <row r="116" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A116" s="156"/>
+      <c r="A116" s="155"/>
       <c r="B116" s="18"/>
       <c r="C116" s="19"/>
       <c r="D116" s="20"/>
@@ -5406,7 +5398,7 @@
       <c r="O116" s="20"/>
     </row>
     <row r="117" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A117" s="156"/>
+      <c r="A117" s="155"/>
       <c r="B117" s="18"/>
       <c r="C117" s="19"/>
       <c r="D117" s="20"/>
@@ -5423,7 +5415,7 @@
       <c r="O117" s="20"/>
     </row>
     <row r="118" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A118" s="156"/>
+      <c r="A118" s="155"/>
       <c r="B118" s="18"/>
       <c r="C118" s="19"/>
       <c r="D118" s="20"/>
@@ -5440,7 +5432,7 @@
       <c r="O118" s="20"/>
     </row>
     <row r="119" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A119" s="156"/>
+      <c r="A119" s="155"/>
       <c r="B119" s="18"/>
       <c r="C119" s="19"/>
       <c r="D119" s="20"/>
@@ -5457,7 +5449,7 @@
       <c r="O119" s="20"/>
     </row>
     <row r="120" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A120" s="156"/>
+      <c r="A120" s="155"/>
       <c r="B120" s="18"/>
       <c r="C120" s="19"/>
       <c r="D120" s="20"/>
@@ -5474,7 +5466,7 @@
       <c r="O120" s="20"/>
     </row>
     <row r="121" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A121" s="156"/>
+      <c r="A121" s="155"/>
       <c r="B121" s="18"/>
       <c r="C121" s="19"/>
       <c r="D121" s="20"/>
@@ -5491,7 +5483,7 @@
       <c r="O121" s="20"/>
     </row>
     <row r="122" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A122" s="156"/>
+      <c r="A122" s="155"/>
       <c r="B122" s="18"/>
       <c r="C122" s="19"/>
       <c r="D122" s="20"/>
@@ -5508,7 +5500,7 @@
       <c r="O122" s="20"/>
     </row>
     <row r="123" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A123" s="156"/>
+      <c r="A123" s="155"/>
       <c r="B123" s="18"/>
       <c r="C123" s="19"/>
       <c r="D123" s="20"/>
@@ -5525,7 +5517,7 @@
       <c r="O123" s="20"/>
     </row>
     <row r="124" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A124" s="156"/>
+      <c r="A124" s="155"/>
       <c r="B124" s="18"/>
       <c r="C124" s="19"/>
       <c r="D124" s="20"/>
@@ -5542,7 +5534,7 @@
       <c r="O124" s="20"/>
     </row>
     <row r="125" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A125" s="156"/>
+      <c r="A125" s="155"/>
       <c r="B125" s="18"/>
       <c r="C125" s="19"/>
       <c r="D125" s="20"/>
@@ -5559,7 +5551,7 @@
       <c r="O125" s="20"/>
     </row>
     <row r="126" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A126" s="156"/>
+      <c r="A126" s="155"/>
       <c r="B126" s="18"/>
       <c r="C126" s="19"/>
       <c r="D126" s="20"/>
@@ -5576,7 +5568,7 @@
       <c r="O126" s="20"/>
     </row>
     <row r="127" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A127" s="156"/>
+      <c r="A127" s="155"/>
       <c r="B127" s="18"/>
       <c r="C127" s="19"/>
       <c r="D127" s="20"/>
@@ -5593,7 +5585,7 @@
       <c r="O127" s="20"/>
     </row>
     <row r="128" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A128" s="156"/>
+      <c r="A128" s="155"/>
       <c r="B128" s="18"/>
       <c r="C128" s="19"/>
       <c r="D128" s="20"/>
@@ -5610,7 +5602,7 @@
       <c r="O128" s="20"/>
     </row>
     <row r="129" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A129" s="156"/>
+      <c r="A129" s="155"/>
       <c r="B129" s="18"/>
       <c r="C129" s="19"/>
       <c r="D129" s="20"/>
@@ -5627,7 +5619,7 @@
       <c r="O129" s="20"/>
     </row>
     <row r="130" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A130" s="156"/>
+      <c r="A130" s="155"/>
       <c r="B130" s="18"/>
       <c r="C130" s="19"/>
       <c r="D130" s="20"/>
@@ -5644,7 +5636,7 @@
       <c r="O130" s="20"/>
     </row>
     <row r="131" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A131" s="156"/>
+      <c r="A131" s="155"/>
       <c r="B131" s="18"/>
       <c r="C131" s="19"/>
       <c r="D131" s="20"/>
@@ -5661,7 +5653,7 @@
       <c r="O131" s="20"/>
     </row>
     <row r="132" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A132" s="156"/>
+      <c r="A132" s="155"/>
       <c r="B132" s="18"/>
       <c r="C132" s="19"/>
       <c r="D132" s="20"/>
@@ -5678,7 +5670,7 @@
       <c r="O132" s="20"/>
     </row>
     <row r="133" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A133" s="156"/>
+      <c r="A133" s="155"/>
       <c r="B133" s="18"/>
       <c r="C133" s="19"/>
       <c r="D133" s="20"/>
@@ -5695,7 +5687,7 @@
       <c r="O133" s="20"/>
     </row>
     <row r="134" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A134" s="156"/>
+      <c r="A134" s="155"/>
       <c r="B134" s="18"/>
       <c r="C134" s="19"/>
       <c r="D134" s="20"/>
@@ -5712,7 +5704,7 @@
       <c r="O134" s="20"/>
     </row>
     <row r="135" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A135" s="156"/>
+      <c r="A135" s="155"/>
       <c r="B135" s="18"/>
       <c r="C135" s="19"/>
       <c r="D135" s="20"/>
@@ -5729,7 +5721,7 @@
       <c r="O135" s="20"/>
     </row>
     <row r="136" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A136" s="156"/>
+      <c r="A136" s="155"/>
       <c r="B136" s="18"/>
       <c r="C136" s="19"/>
       <c r="D136" s="20"/>
@@ -5746,7 +5738,7 @@
       <c r="O136" s="20"/>
     </row>
     <row r="137" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A137" s="156"/>
+      <c r="A137" s="155"/>
       <c r="B137" s="18"/>
       <c r="C137" s="19"/>
       <c r="D137" s="20"/>
@@ -5763,7 +5755,7 @@
       <c r="O137" s="20"/>
     </row>
     <row r="138" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A138" s="156"/>
+      <c r="A138" s="155"/>
       <c r="B138" s="18"/>
       <c r="C138" s="19"/>
       <c r="D138" s="20"/>
@@ -5780,7 +5772,7 @@
       <c r="O138" s="20"/>
     </row>
     <row r="139" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A139" s="156"/>
+      <c r="A139" s="155"/>
       <c r="B139" s="18"/>
       <c r="C139" s="19"/>
       <c r="D139" s="20"/>
@@ -5797,7 +5789,7 @@
       <c r="O139" s="20"/>
     </row>
     <row r="140" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A140" s="156"/>
+      <c r="A140" s="155"/>
       <c r="B140" s="18"/>
       <c r="C140" s="19"/>
       <c r="D140" s="20"/>
@@ -5814,7 +5806,7 @@
       <c r="O140" s="20"/>
     </row>
     <row r="141" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A141" s="156"/>
+      <c r="A141" s="155"/>
       <c r="B141" s="18"/>
       <c r="C141" s="19"/>
       <c r="D141" s="20"/>
@@ -5831,7 +5823,7 @@
       <c r="O141" s="20"/>
     </row>
     <row r="142" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A142" s="156"/>
+      <c r="A142" s="155"/>
       <c r="B142" s="18"/>
       <c r="C142" s="19"/>
       <c r="D142" s="20"/>
@@ -5848,7 +5840,7 @@
       <c r="O142" s="20"/>
     </row>
     <row r="143" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A143" s="156"/>
+      <c r="A143" s="155"/>
       <c r="B143" s="18"/>
       <c r="C143" s="19"/>
       <c r="D143" s="20"/>
@@ -5865,7 +5857,7 @@
       <c r="O143" s="20"/>
     </row>
     <row r="144" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A144" s="156"/>
+      <c r="A144" s="155"/>
       <c r="B144" s="18"/>
       <c r="C144" s="19"/>
       <c r="D144" s="20"/>
@@ -5882,7 +5874,7 @@
       <c r="O144" s="20"/>
     </row>
     <row r="145" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A145" s="156"/>
+      <c r="A145" s="155"/>
       <c r="B145" s="18"/>
       <c r="C145" s="19"/>
       <c r="D145" s="20"/>
@@ -5899,7 +5891,7 @@
       <c r="O145" s="20"/>
     </row>
     <row r="146" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A146" s="156"/>
+      <c r="A146" s="155"/>
       <c r="B146" s="18"/>
       <c r="C146" s="19"/>
       <c r="D146" s="20"/>
@@ -5916,7 +5908,7 @@
       <c r="O146" s="20"/>
     </row>
     <row r="147" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A147" s="156"/>
+      <c r="A147" s="155"/>
       <c r="B147" s="18"/>
       <c r="C147" s="19"/>
       <c r="D147" s="20"/>
@@ -5933,7 +5925,7 @@
       <c r="O147" s="20"/>
     </row>
     <row r="148" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A148" s="156"/>
+      <c r="A148" s="155"/>
       <c r="B148" s="18"/>
       <c r="C148" s="19"/>
       <c r="D148" s="20"/>
@@ -5950,7 +5942,7 @@
       <c r="O148" s="20"/>
     </row>
     <row r="149" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A149" s="156"/>
+      <c r="A149" s="155"/>
       <c r="B149" s="18"/>
       <c r="C149" s="19"/>
       <c r="D149" s="20"/>
@@ -5967,7 +5959,7 @@
       <c r="O149" s="20"/>
     </row>
     <row r="150" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A150" s="156"/>
+      <c r="A150" s="155"/>
       <c r="B150" s="18"/>
       <c r="C150" s="19"/>
       <c r="D150" s="20"/>
@@ -5984,7 +5976,7 @@
       <c r="O150" s="20"/>
     </row>
     <row r="151" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A151" s="156"/>
+      <c r="A151" s="155"/>
       <c r="B151" s="18"/>
       <c r="C151" s="19"/>
       <c r="D151" s="20"/>
@@ -6001,7 +5993,7 @@
       <c r="O151" s="20"/>
     </row>
     <row r="152" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A152" s="156"/>
+      <c r="A152" s="155"/>
       <c r="B152" s="18"/>
       <c r="C152" s="19"/>
       <c r="D152" s="20"/>
@@ -6018,7 +6010,7 @@
       <c r="O152" s="20"/>
     </row>
     <row r="153" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A153" s="156"/>
+      <c r="A153" s="155"/>
       <c r="B153" s="18"/>
       <c r="C153" s="19"/>
       <c r="D153" s="20"/>
@@ -6035,7 +6027,7 @@
       <c r="O153" s="20"/>
     </row>
     <row r="154" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A154" s="156"/>
+      <c r="A154" s="155"/>
       <c r="B154" s="18"/>
       <c r="C154" s="19"/>
       <c r="D154" s="20"/>
@@ -6052,7 +6044,7 @@
       <c r="O154" s="20"/>
     </row>
     <row r="155" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A155" s="156"/>
+      <c r="A155" s="155"/>
       <c r="B155" s="18"/>
       <c r="C155" s="19"/>
       <c r="D155" s="20"/>
@@ -6069,7 +6061,7 @@
       <c r="O155" s="20"/>
     </row>
     <row r="156" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A156" s="156"/>
+      <c r="A156" s="155"/>
       <c r="B156" s="18"/>
       <c r="C156" s="19"/>
       <c r="D156" s="20"/>
@@ -6086,7 +6078,7 @@
       <c r="O156" s="20"/>
     </row>
     <row r="157" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A157" s="156"/>
+      <c r="A157" s="155"/>
       <c r="B157" s="18"/>
       <c r="C157" s="19"/>
       <c r="D157" s="20"/>
@@ -6103,7 +6095,7 @@
       <c r="O157" s="20"/>
     </row>
     <row r="158" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A158" s="156"/>
+      <c r="A158" s="155"/>
       <c r="B158" s="18"/>
       <c r="C158" s="19"/>
       <c r="D158" s="20"/>
@@ -6120,7 +6112,7 @@
       <c r="O158" s="20"/>
     </row>
     <row r="159" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A159" s="156"/>
+      <c r="A159" s="155"/>
       <c r="B159" s="18"/>
       <c r="C159" s="19"/>
       <c r="D159" s="20"/>
@@ -6137,7 +6129,7 @@
       <c r="O159" s="20"/>
     </row>
     <row r="160" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A160" s="156"/>
+      <c r="A160" s="155"/>
       <c r="B160" s="18"/>
       <c r="C160" s="19"/>
       <c r="D160" s="20"/>
@@ -6154,7 +6146,7 @@
       <c r="O160" s="20"/>
     </row>
     <row r="161" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A161" s="156"/>
+      <c r="A161" s="155"/>
       <c r="B161" s="18"/>
       <c r="C161" s="19"/>
       <c r="D161" s="20"/>
@@ -6171,7 +6163,7 @@
       <c r="O161" s="20"/>
     </row>
     <row r="162" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A162" s="156"/>
+      <c r="A162" s="155"/>
       <c r="B162" s="18"/>
       <c r="C162" s="19"/>
       <c r="D162" s="20"/>
@@ -6188,7 +6180,7 @@
       <c r="O162" s="20"/>
     </row>
     <row r="163" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A163" s="156"/>
+      <c r="A163" s="155"/>
       <c r="B163" s="18"/>
       <c r="C163" s="19"/>
       <c r="D163" s="20"/>
@@ -6205,7 +6197,7 @@
       <c r="O163" s="20"/>
     </row>
     <row r="164" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A164" s="156"/>
+      <c r="A164" s="155"/>
       <c r="B164" s="18"/>
       <c r="C164" s="19"/>
       <c r="D164" s="20"/>
@@ -6222,7 +6214,7 @@
       <c r="O164" s="20"/>
     </row>
     <row r="165" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A165" s="156"/>
+      <c r="A165" s="155"/>
       <c r="B165" s="18"/>
       <c r="C165" s="19"/>
       <c r="D165" s="20"/>
@@ -6239,7 +6231,7 @@
       <c r="O165" s="20"/>
     </row>
     <row r="166" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A166" s="156"/>
+      <c r="A166" s="155"/>
       <c r="B166" s="18"/>
       <c r="C166" s="19"/>
       <c r="D166" s="20"/>
@@ -6256,7 +6248,7 @@
       <c r="O166" s="20"/>
     </row>
     <row r="167" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A167" s="156"/>
+      <c r="A167" s="155"/>
       <c r="B167" s="18"/>
       <c r="C167" s="19"/>
       <c r="D167" s="20"/>
@@ -6273,7 +6265,7 @@
       <c r="O167" s="20"/>
     </row>
     <row r="168" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A168" s="156"/>
+      <c r="A168" s="155"/>
       <c r="B168" s="18"/>
       <c r="C168" s="19"/>
       <c r="D168" s="20"/>
@@ -6290,7 +6282,7 @@
       <c r="O168" s="20"/>
     </row>
     <row r="169" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A169" s="156"/>
+      <c r="A169" s="155"/>
       <c r="B169" s="18"/>
       <c r="C169" s="19"/>
       <c r="D169" s="20"/>
@@ -6307,7 +6299,7 @@
       <c r="O169" s="20"/>
     </row>
     <row r="170" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A170" s="156"/>
+      <c r="A170" s="155"/>
       <c r="B170" s="18"/>
       <c r="C170" s="19"/>
       <c r="D170" s="20"/>
@@ -6324,7 +6316,7 @@
       <c r="O170" s="20"/>
     </row>
     <row r="171" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A171" s="156"/>
+      <c r="A171" s="155"/>
       <c r="B171" s="18"/>
       <c r="C171" s="19"/>
       <c r="D171" s="20"/>
@@ -6341,7 +6333,7 @@
       <c r="O171" s="20"/>
     </row>
     <row r="172" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A172" s="156"/>
+      <c r="A172" s="155"/>
       <c r="B172" s="18"/>
       <c r="C172" s="19"/>
       <c r="D172" s="20"/>
@@ -6358,7 +6350,7 @@
       <c r="O172" s="20"/>
     </row>
     <row r="173" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A173" s="156"/>
+      <c r="A173" s="155"/>
       <c r="B173" s="18"/>
       <c r="C173" s="19"/>
       <c r="D173" s="20"/>
@@ -6375,7 +6367,7 @@
       <c r="O173" s="20"/>
     </row>
     <row r="174" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A174" s="156"/>
+      <c r="A174" s="155"/>
       <c r="B174" s="18"/>
       <c r="C174" s="19"/>
       <c r="D174" s="20"/>
@@ -6392,7 +6384,7 @@
       <c r="O174" s="20"/>
     </row>
     <row r="175" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A175" s="156"/>
+      <c r="A175" s="155"/>
       <c r="B175" s="18"/>
       <c r="C175" s="19"/>
       <c r="D175" s="20"/>
@@ -6409,7 +6401,7 @@
       <c r="O175" s="20"/>
     </row>
     <row r="176" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A176" s="156"/>
+      <c r="A176" s="155"/>
       <c r="B176" s="18"/>
       <c r="C176" s="19"/>
       <c r="D176" s="20"/>
@@ -6426,7 +6418,7 @@
       <c r="O176" s="20"/>
     </row>
     <row r="177" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A177" s="156"/>
+      <c r="A177" s="155"/>
       <c r="B177" s="18"/>
       <c r="C177" s="19"/>
       <c r="D177" s="20"/>
@@ -6443,7 +6435,7 @@
       <c r="O177" s="20"/>
     </row>
     <row r="178" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A178" s="156"/>
+      <c r="A178" s="155"/>
       <c r="B178" s="18"/>
       <c r="C178" s="19"/>
       <c r="D178" s="20"/>
@@ -6460,7 +6452,7 @@
       <c r="O178" s="20"/>
     </row>
     <row r="179" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A179" s="156"/>
+      <c r="A179" s="155"/>
       <c r="B179" s="18"/>
       <c r="C179" s="19"/>
       <c r="D179" s="20"/>
@@ -6477,7 +6469,7 @@
       <c r="O179" s="20"/>
     </row>
     <row r="180" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A180" s="156"/>
+      <c r="A180" s="155"/>
       <c r="B180" s="18"/>
       <c r="C180" s="19"/>
       <c r="D180" s="20"/>
@@ -6494,7 +6486,7 @@
       <c r="O180" s="20"/>
     </row>
     <row r="181" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A181" s="156"/>
+      <c r="A181" s="155"/>
       <c r="B181" s="18"/>
       <c r="C181" s="19"/>
       <c r="D181" s="20"/>
@@ -6511,7 +6503,7 @@
       <c r="O181" s="20"/>
     </row>
     <row r="182" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A182" s="156"/>
+      <c r="A182" s="155"/>
       <c r="B182" s="18"/>
       <c r="C182" s="19"/>
       <c r="D182" s="20"/>
@@ -6528,7 +6520,7 @@
       <c r="O182" s="20"/>
     </row>
     <row r="183" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A183" s="156"/>
+      <c r="A183" s="155"/>
       <c r="B183" s="18"/>
       <c r="C183" s="19"/>
       <c r="D183" s="20"/>
@@ -6545,7 +6537,7 @@
       <c r="O183" s="20"/>
     </row>
     <row r="184" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A184" s="156"/>
+      <c r="A184" s="155"/>
       <c r="B184" s="18"/>
       <c r="C184" s="19"/>
       <c r="D184" s="20"/>
@@ -6562,7 +6554,7 @@
       <c r="O184" s="20"/>
     </row>
     <row r="185" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A185" s="156"/>
+      <c r="A185" s="155"/>
       <c r="B185" s="18"/>
       <c r="C185" s="19"/>
       <c r="D185" s="20"/>
@@ -6579,7 +6571,7 @@
       <c r="O185" s="20"/>
     </row>
     <row r="186" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A186" s="156"/>
+      <c r="A186" s="155"/>
       <c r="B186" s="18"/>
       <c r="C186" s="19"/>
       <c r="D186" s="20"/>
@@ -6596,7 +6588,7 @@
       <c r="O186" s="20"/>
     </row>
     <row r="187" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A187" s="156"/>
+      <c r="A187" s="155"/>
       <c r="B187" s="18"/>
       <c r="C187" s="19"/>
       <c r="D187" s="20"/>
@@ -6613,7 +6605,7 @@
       <c r="O187" s="20"/>
     </row>
     <row r="188" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A188" s="156"/>
+      <c r="A188" s="155"/>
       <c r="B188" s="18"/>
       <c r="C188" s="19"/>
       <c r="D188" s="20"/>
@@ -6630,7 +6622,7 @@
       <c r="O188" s="20"/>
     </row>
     <row r="189" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A189" s="156"/>
+      <c r="A189" s="155"/>
       <c r="B189" s="18"/>
       <c r="C189" s="19"/>
       <c r="D189" s="20"/>
@@ -6647,7 +6639,7 @@
       <c r="O189" s="20"/>
     </row>
     <row r="190" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A190" s="156"/>
+      <c r="A190" s="155"/>
       <c r="B190" s="18"/>
       <c r="C190" s="19"/>
       <c r="D190" s="20"/>
@@ -6664,7 +6656,7 @@
       <c r="O190" s="20"/>
     </row>
     <row r="191" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A191" s="156"/>
+      <c r="A191" s="155"/>
       <c r="B191" s="18"/>
       <c r="C191" s="19"/>
       <c r="D191" s="20"/>
@@ -6681,7 +6673,7 @@
       <c r="O191" s="20"/>
     </row>
     <row r="192" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A192" s="156"/>
+      <c r="A192" s="155"/>
       <c r="B192" s="18"/>
       <c r="C192" s="19"/>
       <c r="D192" s="20"/>
@@ -6698,7 +6690,7 @@
       <c r="O192" s="20"/>
     </row>
     <row r="193" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A193" s="156"/>
+      <c r="A193" s="155"/>
       <c r="B193" s="18"/>
       <c r="C193" s="19"/>
       <c r="D193" s="20"/>
@@ -6715,7 +6707,7 @@
       <c r="O193" s="20"/>
     </row>
     <row r="194" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A194" s="156"/>
+      <c r="A194" s="155"/>
       <c r="B194" s="18"/>
       <c r="C194" s="19"/>
       <c r="D194" s="20"/>
@@ -6732,7 +6724,7 @@
       <c r="O194" s="20"/>
     </row>
     <row r="195" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A195" s="156"/>
+      <c r="A195" s="155"/>
       <c r="B195" s="18"/>
       <c r="C195" s="19"/>
       <c r="D195" s="20"/>
@@ -6749,7 +6741,7 @@
       <c r="O195" s="20"/>
     </row>
     <row r="196" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A196" s="156"/>
+      <c r="A196" s="155"/>
       <c r="B196" s="18"/>
       <c r="C196" s="19"/>
       <c r="D196" s="20"/>
@@ -6766,7 +6758,7 @@
       <c r="O196" s="20"/>
     </row>
     <row r="197" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A197" s="156"/>
+      <c r="A197" s="155"/>
       <c r="B197" s="18"/>
       <c r="C197" s="19"/>
       <c r="D197" s="20"/>
@@ -6783,7 +6775,7 @@
       <c r="O197" s="20"/>
     </row>
     <row r="198" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A198" s="156"/>
+      <c r="A198" s="155"/>
       <c r="B198" s="18"/>
       <c r="C198" s="19"/>
       <c r="D198" s="20"/>
@@ -6800,7 +6792,7 @@
       <c r="O198" s="20"/>
     </row>
     <row r="199" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A199" s="156"/>
+      <c r="A199" s="155"/>
       <c r="B199" s="18"/>
       <c r="C199" s="19"/>
       <c r="D199" s="20"/>
@@ -6817,7 +6809,7 @@
       <c r="O199" s="20"/>
     </row>
     <row r="200" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A200" s="156"/>
+      <c r="A200" s="155"/>
       <c r="B200" s="18"/>
       <c r="C200" s="19"/>
       <c r="D200" s="20"/>
@@ -6834,7 +6826,7 @@
       <c r="O200" s="20"/>
     </row>
     <row r="201" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A201" s="156"/>
+      <c r="A201" s="155"/>
       <c r="B201" s="18"/>
       <c r="C201" s="19"/>
       <c r="D201" s="20"/>
@@ -6851,7 +6843,7 @@
       <c r="O201" s="20"/>
     </row>
     <row r="202" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A202" s="156"/>
+      <c r="A202" s="155"/>
       <c r="B202" s="18"/>
       <c r="C202" s="19"/>
       <c r="D202" s="20"/>
@@ -6868,7 +6860,7 @@
       <c r="O202" s="20"/>
     </row>
     <row r="203" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A203" s="156"/>
+      <c r="A203" s="155"/>
       <c r="B203" s="18"/>
       <c r="C203" s="19"/>
       <c r="D203" s="20"/>
@@ -6885,7 +6877,7 @@
       <c r="O203" s="20"/>
     </row>
     <row r="204" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A204" s="156"/>
+      <c r="A204" s="155"/>
       <c r="B204" s="18"/>
       <c r="C204" s="19"/>
       <c r="D204" s="20"/>
@@ -6902,7 +6894,7 @@
       <c r="O204" s="20"/>
     </row>
     <row r="205" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A205" s="156"/>
+      <c r="A205" s="155"/>
       <c r="B205" s="18"/>
       <c r="C205" s="19"/>
       <c r="D205" s="20"/>
@@ -6919,7 +6911,7 @@
       <c r="O205" s="20"/>
     </row>
     <row r="206" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A206" s="156"/>
+      <c r="A206" s="155"/>
       <c r="B206" s="18"/>
       <c r="C206" s="19"/>
       <c r="D206" s="20"/>
@@ -6936,7 +6928,7 @@
       <c r="O206" s="20"/>
     </row>
     <row r="207" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A207" s="156"/>
+      <c r="A207" s="155"/>
       <c r="B207" s="18"/>
       <c r="C207" s="19"/>
       <c r="D207" s="20"/>
@@ -6953,7 +6945,7 @@
       <c r="O207" s="20"/>
     </row>
     <row r="208" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A208" s="156"/>
+      <c r="A208" s="155"/>
       <c r="B208" s="18"/>
       <c r="C208" s="19"/>
       <c r="D208" s="20"/>
@@ -6970,7 +6962,7 @@
       <c r="O208" s="20"/>
     </row>
     <row r="209" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A209" s="156"/>
+      <c r="A209" s="155"/>
       <c r="B209" s="18"/>
       <c r="C209" s="19"/>
       <c r="D209" s="20"/>
@@ -6987,7 +6979,7 @@
       <c r="O209" s="20"/>
     </row>
     <row r="210" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A210" s="156"/>
+      <c r="A210" s="155"/>
       <c r="B210" s="18"/>
       <c r="C210" s="19"/>
       <c r="D210" s="20"/>
@@ -7004,7 +6996,7 @@
       <c r="O210" s="20"/>
     </row>
     <row r="211" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A211" s="156"/>
+      <c r="A211" s="155"/>
       <c r="B211" s="18"/>
       <c r="C211" s="19"/>
       <c r="D211" s="20"/>
@@ -7021,7 +7013,7 @@
       <c r="O211" s="20"/>
     </row>
     <row r="212" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A212" s="156"/>
+      <c r="A212" s="155"/>
       <c r="B212" s="18"/>
       <c r="C212" s="19"/>
       <c r="D212" s="20"/>
@@ -7038,7 +7030,7 @@
       <c r="O212" s="20"/>
     </row>
     <row r="213" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A213" s="156"/>
+      <c r="A213" s="155"/>
       <c r="B213" s="18"/>
       <c r="C213" s="19"/>
       <c r="D213" s="20"/>
@@ -7055,7 +7047,7 @@
       <c r="O213" s="20"/>
     </row>
     <row r="214" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A214" s="156"/>
+      <c r="A214" s="155"/>
       <c r="B214" s="18"/>
       <c r="C214" s="19"/>
       <c r="D214" s="20"/>
@@ -7072,7 +7064,7 @@
       <c r="O214" s="20"/>
     </row>
     <row r="215" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A215" s="156"/>
+      <c r="A215" s="155"/>
       <c r="B215" s="18"/>
       <c r="C215" s="19"/>
       <c r="D215" s="20"/>
@@ -7089,7 +7081,7 @@
       <c r="O215" s="20"/>
     </row>
     <row r="216" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A216" s="156"/>
+      <c r="A216" s="155"/>
       <c r="B216" s="18"/>
       <c r="C216" s="19"/>
       <c r="D216" s="20"/>
@@ -7106,7 +7098,7 @@
       <c r="O216" s="20"/>
     </row>
     <row r="217" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A217" s="156"/>
+      <c r="A217" s="155"/>
       <c r="B217" s="18"/>
       <c r="C217" s="19"/>
       <c r="D217" s="20"/>
@@ -7123,7 +7115,7 @@
       <c r="O217" s="20"/>
     </row>
     <row r="218" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A218" s="156"/>
+      <c r="A218" s="155"/>
       <c r="B218" s="18"/>
       <c r="C218" s="19"/>
       <c r="D218" s="20"/>
@@ -7140,7 +7132,7 @@
       <c r="O218" s="20"/>
     </row>
     <row r="219" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A219" s="156"/>
+      <c r="A219" s="155"/>
       <c r="B219" s="18"/>
       <c r="C219" s="19"/>
       <c r="D219" s="20"/>
@@ -7157,7 +7149,7 @@
       <c r="O219" s="20"/>
     </row>
     <row r="220" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A220" s="156"/>
+      <c r="A220" s="155"/>
       <c r="B220" s="18"/>
       <c r="C220" s="19"/>
       <c r="D220" s="20"/>
@@ -7174,7 +7166,7 @@
       <c r="O220" s="20"/>
     </row>
     <row r="221" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A221" s="156"/>
+      <c r="A221" s="155"/>
       <c r="B221" s="18"/>
       <c r="C221" s="19"/>
       <c r="D221" s="20"/>
@@ -7191,7 +7183,7 @@
       <c r="O221" s="20"/>
     </row>
     <row r="222" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A222" s="156"/>
+      <c r="A222" s="155"/>
       <c r="B222" s="18"/>
       <c r="C222" s="19"/>
       <c r="D222" s="20"/>
@@ -7208,7 +7200,7 @@
       <c r="O222" s="20"/>
     </row>
     <row r="223" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A223" s="156"/>
+      <c r="A223" s="155"/>
       <c r="B223" s="18"/>
       <c r="C223" s="19"/>
       <c r="D223" s="20"/>
@@ -7225,7 +7217,7 @@
       <c r="O223" s="20"/>
     </row>
     <row r="224" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A224" s="156"/>
+      <c r="A224" s="155"/>
       <c r="B224" s="18"/>
       <c r="C224" s="19"/>
       <c r="D224" s="20"/>
@@ -7242,7 +7234,7 @@
       <c r="O224" s="20"/>
     </row>
     <row r="225" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A225" s="156"/>
+      <c r="A225" s="155"/>
       <c r="B225" s="18"/>
       <c r="C225" s="19"/>
       <c r="D225" s="20"/>
@@ -7259,7 +7251,7 @@
       <c r="O225" s="20"/>
     </row>
     <row r="226" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A226" s="156"/>
+      <c r="A226" s="155"/>
       <c r="B226" s="18"/>
       <c r="C226" s="19"/>
       <c r="D226" s="20"/>
@@ -7276,7 +7268,7 @@
       <c r="O226" s="20"/>
     </row>
     <row r="227" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A227" s="156"/>
+      <c r="A227" s="155"/>
       <c r="B227" s="18"/>
       <c r="C227" s="19"/>
       <c r="D227" s="20"/>
@@ -7293,7 +7285,7 @@
       <c r="O227" s="20"/>
     </row>
     <row r="228" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A228" s="156"/>
+      <c r="A228" s="155"/>
       <c r="B228" s="18"/>
       <c r="C228" s="19"/>
       <c r="D228" s="20"/>
@@ -7310,7 +7302,7 @@
       <c r="O228" s="20"/>
     </row>
     <row r="229" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A229" s="156"/>
+      <c r="A229" s="155"/>
       <c r="B229" s="18"/>
       <c r="C229" s="19"/>
       <c r="D229" s="20"/>
@@ -7327,7 +7319,7 @@
       <c r="O229" s="20"/>
     </row>
     <row r="230" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A230" s="156"/>
+      <c r="A230" s="155"/>
       <c r="B230" s="18"/>
       <c r="C230" s="19"/>
       <c r="D230" s="20"/>
@@ -7344,7 +7336,7 @@
       <c r="O230" s="20"/>
     </row>
     <row r="231" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A231" s="156"/>
+      <c r="A231" s="155"/>
       <c r="B231" s="18"/>
       <c r="C231" s="19"/>
       <c r="D231" s="20"/>
@@ -7361,7 +7353,7 @@
       <c r="O231" s="20"/>
     </row>
     <row r="232" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A232" s="156"/>
+      <c r="A232" s="155"/>
       <c r="B232" s="18"/>
       <c r="C232" s="19"/>
       <c r="D232" s="20"/>
@@ -7378,7 +7370,7 @@
       <c r="O232" s="20"/>
     </row>
     <row r="233" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A233" s="156"/>
+      <c r="A233" s="155"/>
       <c r="B233" s="18"/>
       <c r="C233" s="19"/>
       <c r="D233" s="20"/>
@@ -7395,7 +7387,7 @@
       <c r="O233" s="20"/>
     </row>
     <row r="234" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A234" s="156"/>
+      <c r="A234" s="155"/>
       <c r="B234" s="18"/>
       <c r="C234" s="19"/>
       <c r="D234" s="20"/>
@@ -7412,7 +7404,7 @@
       <c r="O234" s="20"/>
     </row>
     <row r="235" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A235" s="156"/>
+      <c r="A235" s="155"/>
       <c r="B235" s="18"/>
       <c r="C235" s="19"/>
       <c r="D235" s="20"/>
@@ -7429,7 +7421,7 @@
       <c r="O235" s="20"/>
     </row>
     <row r="236" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A236" s="156"/>
+      <c r="A236" s="155"/>
       <c r="B236" s="18"/>
       <c r="C236" s="19"/>
       <c r="D236" s="20"/>
@@ -7446,7 +7438,7 @@
       <c r="O236" s="20"/>
     </row>
     <row r="237" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A237" s="156"/>
+      <c r="A237" s="155"/>
       <c r="B237" s="18"/>
       <c r="C237" s="19"/>
       <c r="D237" s="20"/>
@@ -7463,7 +7455,7 @@
       <c r="O237" s="20"/>
     </row>
     <row r="238" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A238" s="156"/>
+      <c r="A238" s="155"/>
       <c r="B238" s="18"/>
       <c r="C238" s="19"/>
       <c r="D238" s="20"/>
@@ -7480,7 +7472,7 @@
       <c r="O238" s="20"/>
     </row>
     <row r="239" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A239" s="156"/>
+      <c r="A239" s="155"/>
       <c r="B239" s="18"/>
       <c r="C239" s="19"/>
       <c r="D239" s="20"/>
@@ -7497,7 +7489,7 @@
       <c r="O239" s="20"/>
     </row>
     <row r="240" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A240" s="156"/>
+      <c r="A240" s="155"/>
       <c r="B240" s="18"/>
       <c r="C240" s="19"/>
       <c r="D240" s="20"/>
@@ -7514,7 +7506,7 @@
       <c r="O240" s="20"/>
     </row>
     <row r="241" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A241" s="156"/>
+      <c r="A241" s="155"/>
       <c r="B241" s="18"/>
       <c r="C241" s="19"/>
       <c r="D241" s="20"/>
@@ -7531,7 +7523,7 @@
       <c r="O241" s="20"/>
     </row>
     <row r="242" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A242" s="156"/>
+      <c r="A242" s="155"/>
       <c r="B242" s="18"/>
       <c r="C242" s="19"/>
       <c r="D242" s="20"/>
@@ -7548,7 +7540,7 @@
       <c r="O242" s="20"/>
     </row>
     <row r="243" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A243" s="156"/>
+      <c r="A243" s="155"/>
       <c r="B243" s="18"/>
       <c r="C243" s="19"/>
       <c r="D243" s="20"/>
@@ -7565,7 +7557,7 @@
       <c r="O243" s="20"/>
     </row>
     <row r="244" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A244" s="156"/>
+      <c r="A244" s="155"/>
       <c r="B244" s="18"/>
       <c r="C244" s="19"/>
       <c r="D244" s="20"/>
@@ -7582,7 +7574,7 @@
       <c r="O244" s="20"/>
     </row>
     <row r="245" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A245" s="156"/>
+      <c r="A245" s="155"/>
       <c r="B245" s="18"/>
       <c r="C245" s="19"/>
       <c r="D245" s="20"/>
@@ -7599,7 +7591,7 @@
       <c r="O245" s="20"/>
     </row>
     <row r="246" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A246" s="156"/>
+      <c r="A246" s="155"/>
       <c r="B246" s="18"/>
       <c r="C246" s="19"/>
       <c r="D246" s="20"/>
@@ -7616,7 +7608,7 @@
       <c r="O246" s="20"/>
     </row>
     <row r="247" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A247" s="156"/>
+      <c r="A247" s="155"/>
       <c r="B247" s="18"/>
       <c r="C247" s="19"/>
       <c r="D247" s="20"/>
@@ -7633,7 +7625,7 @@
       <c r="O247" s="20"/>
     </row>
     <row r="248" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A248" s="156"/>
+      <c r="A248" s="155"/>
       <c r="B248" s="18"/>
       <c r="C248" s="19"/>
       <c r="D248" s="20"/>
@@ -7650,7 +7642,7 @@
       <c r="O248" s="20"/>
     </row>
     <row r="249" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A249" s="156"/>
+      <c r="A249" s="155"/>
       <c r="B249" s="18"/>
       <c r="C249" s="19"/>
       <c r="D249" s="20"/>
@@ -7667,7 +7659,7 @@
       <c r="O249" s="20"/>
     </row>
     <row r="250" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A250" s="156"/>
+      <c r="A250" s="155"/>
       <c r="B250" s="18"/>
       <c r="C250" s="19"/>
       <c r="D250" s="20"/>
@@ -7684,7 +7676,7 @@
       <c r="O250" s="20"/>
     </row>
     <row r="251" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A251" s="156"/>
+      <c r="A251" s="155"/>
       <c r="B251" s="18"/>
       <c r="C251" s="19"/>
       <c r="D251" s="20"/>
@@ -7701,7 +7693,7 @@
       <c r="O251" s="20"/>
     </row>
     <row r="252" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A252" s="156"/>
+      <c r="A252" s="155"/>
       <c r="B252" s="18"/>
       <c r="C252" s="19"/>
       <c r="D252" s="20"/>
@@ -7718,7 +7710,7 @@
       <c r="O252" s="20"/>
     </row>
     <row r="253" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A253" s="156"/>
+      <c r="A253" s="155"/>
       <c r="B253" s="18"/>
       <c r="C253" s="19"/>
       <c r="D253" s="20"/>
@@ -7735,7 +7727,7 @@
       <c r="O253" s="20"/>
     </row>
     <row r="254" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A254" s="156"/>
+      <c r="A254" s="155"/>
       <c r="B254" s="18"/>
       <c r="C254" s="19"/>
       <c r="D254" s="20"/>
@@ -7752,7 +7744,7 @@
       <c r="O254" s="20"/>
     </row>
     <row r="255" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A255" s="156"/>
+      <c r="A255" s="155"/>
       <c r="B255" s="18"/>
       <c r="C255" s="19"/>
       <c r="D255" s="20"/>
@@ -7769,7 +7761,7 @@
       <c r="O255" s="20"/>
     </row>
     <row r="256" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A256" s="156"/>
+      <c r="A256" s="155"/>
       <c r="B256" s="18"/>
       <c r="C256" s="19"/>
       <c r="D256" s="20"/>
@@ -7786,7 +7778,7 @@
       <c r="O256" s="20"/>
     </row>
     <row r="257" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A257" s="156"/>
+      <c r="A257" s="155"/>
       <c r="B257" s="18"/>
       <c r="C257" s="19"/>
       <c r="D257" s="20"/>
@@ -7803,7 +7795,7 @@
       <c r="O257" s="20"/>
     </row>
     <row r="258" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A258" s="156"/>
+      <c r="A258" s="155"/>
       <c r="B258" s="18"/>
       <c r="C258" s="19"/>
       <c r="D258" s="20"/>
@@ -7820,7 +7812,7 @@
       <c r="O258" s="20"/>
     </row>
     <row r="259" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A259" s="156"/>
+      <c r="A259" s="155"/>
       <c r="B259" s="18"/>
       <c r="C259" s="19"/>
       <c r="D259" s="20"/>
@@ -7837,7 +7829,7 @@
       <c r="O259" s="20"/>
     </row>
     <row r="260" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A260" s="156"/>
+      <c r="A260" s="155"/>
       <c r="B260" s="18"/>
       <c r="C260" s="19"/>
       <c r="D260" s="20"/>
@@ -7854,7 +7846,7 @@
       <c r="O260" s="20"/>
     </row>
     <row r="261" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A261" s="156"/>
+      <c r="A261" s="155"/>
       <c r="B261" s="18"/>
       <c r="C261" s="19"/>
       <c r="D261" s="20"/>
@@ -7871,7 +7863,7 @@
       <c r="O261" s="20"/>
     </row>
     <row r="262" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A262" s="156"/>
+      <c r="A262" s="155"/>
       <c r="B262" s="18"/>
       <c r="C262" s="19"/>
       <c r="D262" s="20"/>
@@ -7888,7 +7880,7 @@
       <c r="O262" s="20"/>
     </row>
     <row r="263" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A263" s="156"/>
+      <c r="A263" s="155"/>
       <c r="B263" s="18"/>
       <c r="C263" s="19"/>
       <c r="D263" s="20"/>
@@ -7905,7 +7897,7 @@
       <c r="O263" s="20"/>
     </row>
     <row r="264" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A264" s="156"/>
+      <c r="A264" s="155"/>
       <c r="B264" s="18"/>
       <c r="C264" s="19"/>
       <c r="D264" s="20"/>
@@ -7922,7 +7914,7 @@
       <c r="O264" s="20"/>
     </row>
     <row r="265" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A265" s="156"/>
+      <c r="A265" s="155"/>
       <c r="B265" s="18"/>
       <c r="C265" s="19"/>
       <c r="D265" s="20"/>
@@ -7939,7 +7931,7 @@
       <c r="O265" s="20"/>
     </row>
     <row r="266" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A266" s="156"/>
+      <c r="A266" s="155"/>
       <c r="B266" s="18"/>
       <c r="C266" s="19"/>
       <c r="D266" s="20"/>
@@ -7956,7 +7948,7 @@
       <c r="O266" s="20"/>
     </row>
     <row r="267" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A267" s="156"/>
+      <c r="A267" s="155"/>
       <c r="B267" s="18"/>
       <c r="C267" s="19"/>
       <c r="D267" s="20"/>
@@ -7973,7 +7965,7 @@
       <c r="O267" s="20"/>
     </row>
     <row r="268" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A268" s="156"/>
+      <c r="A268" s="155"/>
       <c r="B268" s="18"/>
       <c r="C268" s="19"/>
       <c r="D268" s="20"/>
@@ -7990,7 +7982,7 @@
       <c r="O268" s="20"/>
     </row>
     <row r="269" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A269" s="156"/>
+      <c r="A269" s="155"/>
       <c r="B269" s="18"/>
       <c r="C269" s="19"/>
       <c r="D269" s="20"/>
@@ -8007,7 +7999,7 @@
       <c r="O269" s="20"/>
     </row>
     <row r="270" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A270" s="156"/>
+      <c r="A270" s="155"/>
       <c r="B270" s="18"/>
       <c r="C270" s="19"/>
       <c r="D270" s="20"/>
@@ -8024,7 +8016,7 @@
       <c r="O270" s="20"/>
     </row>
     <row r="271" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A271" s="156"/>
+      <c r="A271" s="155"/>
       <c r="B271" s="18"/>
       <c r="C271" s="19"/>
       <c r="D271" s="20"/>
@@ -8041,7 +8033,7 @@
       <c r="O271" s="20"/>
     </row>
     <row r="272" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A272" s="156"/>
+      <c r="A272" s="155"/>
       <c r="B272" s="18"/>
       <c r="C272" s="19"/>
       <c r="D272" s="20"/>
@@ -8058,7 +8050,7 @@
       <c r="O272" s="20"/>
     </row>
     <row r="273" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A273" s="156"/>
+      <c r="A273" s="155"/>
       <c r="B273" s="18"/>
       <c r="C273" s="19"/>
       <c r="D273" s="20"/>
@@ -8075,7 +8067,7 @@
       <c r="O273" s="20"/>
     </row>
     <row r="274" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A274" s="156"/>
+      <c r="A274" s="155"/>
       <c r="B274" s="18"/>
       <c r="C274" s="19"/>
       <c r="D274" s="20"/>
@@ -8092,7 +8084,7 @@
       <c r="O274" s="20"/>
     </row>
     <row r="275" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A275" s="156"/>
+      <c r="A275" s="155"/>
       <c r="B275" s="18"/>
       <c r="C275" s="19"/>
       <c r="D275" s="20"/>
@@ -8109,7 +8101,7 @@
       <c r="O275" s="20"/>
     </row>
     <row r="276" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A276" s="156"/>
+      <c r="A276" s="155"/>
       <c r="B276" s="18"/>
       <c r="C276" s="19"/>
       <c r="D276" s="20"/>
@@ -8126,7 +8118,7 @@
       <c r="O276" s="20"/>
     </row>
     <row r="277" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A277" s="156"/>
+      <c r="A277" s="155"/>
       <c r="B277" s="18"/>
       <c r="C277" s="19"/>
       <c r="D277" s="20"/>
@@ -8143,7 +8135,7 @@
       <c r="O277" s="20"/>
     </row>
     <row r="278" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A278" s="156"/>
+      <c r="A278" s="155"/>
       <c r="B278" s="18"/>
       <c r="C278" s="19"/>
       <c r="D278" s="20"/>
@@ -8160,7 +8152,7 @@
       <c r="O278" s="20"/>
     </row>
     <row r="279" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A279" s="156"/>
+      <c r="A279" s="155"/>
       <c r="B279" s="18"/>
       <c r="C279" s="19"/>
       <c r="D279" s="20"/>
@@ -8177,7 +8169,7 @@
       <c r="O279" s="20"/>
     </row>
     <row r="280" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A280" s="156"/>
+      <c r="A280" s="155"/>
       <c r="B280" s="18"/>
       <c r="C280" s="19"/>
       <c r="D280" s="20"/>
@@ -8194,7 +8186,7 @@
       <c r="O280" s="20"/>
     </row>
     <row r="281" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A281" s="156"/>
+      <c r="A281" s="155"/>
       <c r="B281" s="18"/>
       <c r="C281" s="19"/>
       <c r="D281" s="20"/>
@@ -8211,7 +8203,7 @@
       <c r="O281" s="20"/>
     </row>
     <row r="282" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A282" s="156"/>
+      <c r="A282" s="155"/>
       <c r="B282" s="18"/>
       <c r="C282" s="19"/>
       <c r="D282" s="20"/>
@@ -8228,7 +8220,7 @@
       <c r="O282" s="20"/>
     </row>
     <row r="283" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A283" s="156"/>
+      <c r="A283" s="155"/>
       <c r="B283" s="18"/>
       <c r="C283" s="19"/>
       <c r="D283" s="20"/>
@@ -8245,7 +8237,7 @@
       <c r="O283" s="20"/>
     </row>
     <row r="284" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A284" s="156"/>
+      <c r="A284" s="155"/>
       <c r="B284" s="18"/>
       <c r="C284" s="19"/>
       <c r="D284" s="20"/>
@@ -8262,7 +8254,7 @@
       <c r="O284" s="20"/>
     </row>
     <row r="285" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A285" s="156"/>
+      <c r="A285" s="155"/>
       <c r="B285" s="18"/>
       <c r="C285" s="19"/>
       <c r="D285" s="20"/>
@@ -8279,7 +8271,7 @@
       <c r="O285" s="20"/>
     </row>
     <row r="286" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A286" s="156"/>
+      <c r="A286" s="155"/>
       <c r="B286" s="18"/>
       <c r="C286" s="19"/>
       <c r="D286" s="20"/>
@@ -8296,7 +8288,7 @@
       <c r="O286" s="20"/>
     </row>
     <row r="287" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A287" s="156"/>
+      <c r="A287" s="155"/>
       <c r="B287" s="18"/>
       <c r="C287" s="19"/>
       <c r="D287" s="20"/>
@@ -8313,7 +8305,7 @@
       <c r="O287" s="20"/>
     </row>
     <row r="288" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A288" s="156"/>
+      <c r="A288" s="155"/>
       <c r="B288" s="18"/>
       <c r="C288" s="19"/>
       <c r="D288" s="20"/>
@@ -8330,7 +8322,7 @@
       <c r="O288" s="20"/>
     </row>
     <row r="289" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A289" s="156"/>
+      <c r="A289" s="155"/>
       <c r="B289" s="18"/>
       <c r="C289" s="19"/>
       <c r="D289" s="20"/>
@@ -8347,7 +8339,7 @@
       <c r="O289" s="20"/>
     </row>
     <row r="290" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A290" s="156"/>
+      <c r="A290" s="155"/>
       <c r="B290" s="18"/>
       <c r="C290" s="19"/>
       <c r="D290" s="20"/>
@@ -8364,7 +8356,7 @@
       <c r="O290" s="20"/>
     </row>
     <row r="291" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A291" s="156"/>
+      <c r="A291" s="155"/>
       <c r="B291" s="18"/>
       <c r="C291" s="19"/>
       <c r="D291" s="20"/>
@@ -8381,7 +8373,7 @@
       <c r="O291" s="20"/>
     </row>
     <row r="292" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A292" s="156"/>
+      <c r="A292" s="155"/>
       <c r="B292" s="18"/>
       <c r="C292" s="19"/>
       <c r="D292" s="20"/>
@@ -8398,7 +8390,7 @@
       <c r="O292" s="20"/>
     </row>
     <row r="293" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A293" s="156"/>
+      <c r="A293" s="155"/>
       <c r="B293" s="18"/>
       <c r="C293" s="19"/>
       <c r="D293" s="20"/>
@@ -8415,7 +8407,7 @@
       <c r="O293" s="20"/>
     </row>
     <row r="294" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A294" s="156"/>
+      <c r="A294" s="155"/>
       <c r="B294" s="18"/>
       <c r="C294" s="19"/>
       <c r="D294" s="20"/>
@@ -8432,7 +8424,7 @@
       <c r="O294" s="20"/>
     </row>
     <row r="295" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A295" s="156"/>
+      <c r="A295" s="155"/>
       <c r="B295" s="18"/>
       <c r="C295" s="19"/>
       <c r="D295" s="20"/>
@@ -8449,7 +8441,7 @@
       <c r="O295" s="20"/>
     </row>
     <row r="296" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A296" s="156"/>
+      <c r="A296" s="155"/>
       <c r="B296" s="18"/>
       <c r="C296" s="19"/>
       <c r="D296" s="20"/>
@@ -8466,7 +8458,7 @@
       <c r="O296" s="20"/>
     </row>
     <row r="297" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A297" s="156"/>
+      <c r="A297" s="155"/>
       <c r="B297" s="18"/>
       <c r="C297" s="19"/>
       <c r="D297" s="20"/>
@@ -8483,7 +8475,7 @@
       <c r="O297" s="20"/>
     </row>
     <row r="298" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A298" s="156"/>
+      <c r="A298" s="155"/>
       <c r="B298" s="18"/>
       <c r="C298" s="19"/>
       <c r="D298" s="20"/>
@@ -8500,7 +8492,7 @@
       <c r="O298" s="20"/>
     </row>
     <row r="299" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A299" s="156"/>
+      <c r="A299" s="155"/>
       <c r="B299" s="18"/>
       <c r="C299" s="19"/>
       <c r="D299" s="20"/>
@@ -8517,7 +8509,7 @@
       <c r="O299" s="20"/>
     </row>
     <row r="300" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A300" s="156"/>
+      <c r="A300" s="155"/>
       <c r="B300" s="18"/>
       <c r="C300" s="19"/>
       <c r="D300" s="20"/>
@@ -8534,7 +8526,7 @@
       <c r="O300" s="20"/>
     </row>
     <row r="301" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A301" s="156"/>
+      <c r="A301" s="155"/>
       <c r="B301" s="18"/>
       <c r="C301" s="19"/>
       <c r="D301" s="20"/>
@@ -8551,7 +8543,7 @@
       <c r="O301" s="20"/>
     </row>
     <row r="302" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A302" s="156"/>
+      <c r="A302" s="155"/>
       <c r="B302" s="18"/>
       <c r="C302" s="19"/>
       <c r="D302" s="20"/>
@@ -8568,7 +8560,7 @@
       <c r="O302" s="20"/>
     </row>
     <row r="303" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A303" s="156"/>
+      <c r="A303" s="155"/>
       <c r="B303" s="18"/>
       <c r="C303" s="19"/>
       <c r="D303" s="20"/>
@@ -8585,7 +8577,7 @@
       <c r="O303" s="20"/>
     </row>
     <row r="304" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A304" s="156"/>
+      <c r="A304" s="155"/>
       <c r="B304" s="18"/>
       <c r="C304" s="19"/>
       <c r="D304" s="20"/>
@@ -8602,7 +8594,7 @@
       <c r="O304" s="20"/>
     </row>
     <row r="305" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A305" s="156"/>
+      <c r="A305" s="155"/>
       <c r="B305" s="18"/>
       <c r="C305" s="19"/>
       <c r="D305" s="20"/>
@@ -8619,7 +8611,7 @@
       <c r="O305" s="20"/>
     </row>
     <row r="306" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A306" s="156"/>
+      <c r="A306" s="155"/>
       <c r="B306" s="18"/>
       <c r="C306" s="19"/>
       <c r="D306" s="20"/>
@@ -8636,7 +8628,7 @@
       <c r="O306" s="20"/>
     </row>
     <row r="307" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A307" s="156"/>
+      <c r="A307" s="155"/>
       <c r="B307" s="18"/>
       <c r="C307" s="19"/>
       <c r="D307" s="20"/>
@@ -8653,7 +8645,7 @@
       <c r="O307" s="20"/>
     </row>
     <row r="308" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A308" s="156"/>
+      <c r="A308" s="155"/>
       <c r="B308" s="18"/>
       <c r="C308" s="19"/>
       <c r="D308" s="20"/>
@@ -8670,7 +8662,7 @@
       <c r="O308" s="20"/>
     </row>
     <row r="309" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A309" s="156"/>
+      <c r="A309" s="155"/>
       <c r="B309" s="18"/>
       <c r="C309" s="19"/>
       <c r="D309" s="20"/>
@@ -8687,7 +8679,7 @@
       <c r="O309" s="20"/>
     </row>
     <row r="310" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A310" s="156"/>
+      <c r="A310" s="155"/>
       <c r="B310" s="18"/>
       <c r="C310" s="19"/>
       <c r="D310" s="20"/>
@@ -8704,7 +8696,7 @@
       <c r="O310" s="20"/>
     </row>
     <row r="311" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A311" s="156"/>
+      <c r="A311" s="155"/>
       <c r="B311" s="18"/>
       <c r="C311" s="19"/>
       <c r="D311" s="20"/>
@@ -8721,7 +8713,7 @@
       <c r="O311" s="20"/>
     </row>
     <row r="312" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A312" s="156"/>
+      <c r="A312" s="155"/>
       <c r="B312" s="18"/>
       <c r="C312" s="19"/>
       <c r="D312" s="20"/>
@@ -8738,7 +8730,7 @@
       <c r="O312" s="20"/>
     </row>
     <row r="313" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A313" s="156"/>
+      <c r="A313" s="155"/>
       <c r="B313" s="18"/>
       <c r="C313" s="19"/>
       <c r="D313" s="20"/>
@@ -8755,7 +8747,7 @@
       <c r="O313" s="20"/>
     </row>
     <row r="314" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A314" s="156"/>
+      <c r="A314" s="155"/>
       <c r="B314" s="18"/>
       <c r="C314" s="19"/>
       <c r="D314" s="20"/>
@@ -8772,7 +8764,7 @@
       <c r="O314" s="20"/>
     </row>
     <row r="315" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A315" s="156"/>
+      <c r="A315" s="155"/>
       <c r="B315" s="18"/>
       <c r="C315" s="19"/>
       <c r="D315" s="20"/>
@@ -8789,7 +8781,7 @@
       <c r="O315" s="20"/>
     </row>
     <row r="316" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A316" s="156"/>
+      <c r="A316" s="155"/>
       <c r="B316" s="18"/>
       <c r="C316" s="19"/>
       <c r="D316" s="20"/>
@@ -8806,7 +8798,7 @@
       <c r="O316" s="20"/>
     </row>
     <row r="317" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A317" s="156"/>
+      <c r="A317" s="155"/>
       <c r="B317" s="18"/>
       <c r="C317" s="19"/>
       <c r="D317" s="20"/>
@@ -8823,7 +8815,7 @@
       <c r="O317" s="20"/>
     </row>
     <row r="318" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A318" s="156"/>
+      <c r="A318" s="155"/>
       <c r="B318" s="18"/>
       <c r="C318" s="19"/>
       <c r="D318" s="20"/>
@@ -8840,7 +8832,7 @@
       <c r="O318" s="20"/>
     </row>
     <row r="319" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A319" s="156"/>
+      <c r="A319" s="155"/>
       <c r="B319" s="18"/>
       <c r="C319" s="19"/>
       <c r="D319" s="20"/>
@@ -8857,7 +8849,7 @@
       <c r="O319" s="20"/>
     </row>
     <row r="320" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A320" s="156"/>
+      <c r="A320" s="155"/>
       <c r="B320" s="18"/>
       <c r="C320" s="19"/>
       <c r="D320" s="20"/>
@@ -8874,7 +8866,7 @@
       <c r="O320" s="20"/>
     </row>
     <row r="321" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A321" s="156"/>
+      <c r="A321" s="155"/>
       <c r="B321" s="18"/>
       <c r="C321" s="19"/>
       <c r="D321" s="20"/>
@@ -8891,7 +8883,7 @@
       <c r="O321" s="20"/>
     </row>
     <row r="322" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A322" s="156"/>
+      <c r="A322" s="155"/>
       <c r="B322" s="18"/>
       <c r="C322" s="19"/>
       <c r="D322" s="20"/>
@@ -8908,7 +8900,7 @@
       <c r="O322" s="20"/>
     </row>
     <row r="323" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A323" s="156"/>
+      <c r="A323" s="155"/>
       <c r="B323" s="18"/>
       <c r="C323" s="19"/>
       <c r="D323" s="20"/>
@@ -8925,7 +8917,7 @@
       <c r="O323" s="20"/>
     </row>
     <row r="324" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A324" s="156"/>
+      <c r="A324" s="155"/>
       <c r="B324" s="18"/>
       <c r="C324" s="19"/>
       <c r="D324" s="20"/>
@@ -8942,7 +8934,7 @@
       <c r="O324" s="20"/>
     </row>
     <row r="325" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A325" s="156"/>
+      <c r="A325" s="155"/>
       <c r="B325" s="18"/>
       <c r="C325" s="19"/>
       <c r="D325" s="20"/>
@@ -8959,7 +8951,7 @@
       <c r="O325" s="20"/>
     </row>
     <row r="326" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A326" s="156"/>
+      <c r="A326" s="155"/>
       <c r="B326" s="18"/>
       <c r="C326" s="19"/>
       <c r="D326" s="20"/>
@@ -8976,7 +8968,7 @@
       <c r="O326" s="20"/>
     </row>
     <row r="327" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A327" s="156"/>
+      <c r="A327" s="155"/>
       <c r="B327" s="18"/>
       <c r="C327" s="19"/>
       <c r="D327" s="20"/>
@@ -8993,7 +8985,7 @@
       <c r="O327" s="20"/>
     </row>
     <row r="328" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A328" s="156"/>
+      <c r="A328" s="155"/>
       <c r="B328" s="18"/>
       <c r="C328" s="19"/>
       <c r="D328" s="20"/>
@@ -9010,7 +9002,7 @@
       <c r="O328" s="20"/>
     </row>
     <row r="329" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A329" s="156"/>
+      <c r="A329" s="155"/>
       <c r="B329" s="18"/>
       <c r="C329" s="19"/>
       <c r="D329" s="20"/>
@@ -9027,7 +9019,7 @@
       <c r="O329" s="20"/>
     </row>
     <row r="330" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A330" s="156"/>
+      <c r="A330" s="155"/>
       <c r="B330" s="18"/>
       <c r="C330" s="19"/>
       <c r="D330" s="20"/>
@@ -9044,7 +9036,7 @@
       <c r="O330" s="20"/>
     </row>
     <row r="331" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A331" s="156"/>
+      <c r="A331" s="155"/>
       <c r="B331" s="18"/>
       <c r="C331" s="19"/>
       <c r="D331" s="20"/>
@@ -9061,7 +9053,7 @@
       <c r="O331" s="20"/>
     </row>
     <row r="332" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A332" s="156"/>
+      <c r="A332" s="155"/>
       <c r="B332" s="18"/>
       <c r="C332" s="19"/>
       <c r="D332" s="20"/>
@@ -9078,7 +9070,7 @@
       <c r="O332" s="20"/>
     </row>
     <row r="333" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A333" s="156"/>
+      <c r="A333" s="155"/>
       <c r="B333" s="18"/>
       <c r="C333" s="19"/>
       <c r="D333" s="20"/>
@@ -9095,7 +9087,7 @@
       <c r="O333" s="20"/>
     </row>
     <row r="334" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A334" s="156"/>
+      <c r="A334" s="155"/>
       <c r="B334" s="18"/>
       <c r="C334" s="19"/>
       <c r="D334" s="20"/>
@@ -9112,7 +9104,7 @@
       <c r="O334" s="20"/>
     </row>
     <row r="335" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A335" s="156"/>
+      <c r="A335" s="155"/>
       <c r="B335" s="18"/>
       <c r="C335" s="19"/>
       <c r="D335" s="20"/>
@@ -9129,7 +9121,7 @@
       <c r="O335" s="20"/>
     </row>
     <row r="336" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A336" s="156"/>
+      <c r="A336" s="155"/>
       <c r="B336" s="18"/>
       <c r="C336" s="19"/>
       <c r="D336" s="20"/>
@@ -9146,7 +9138,7 @@
       <c r="O336" s="20"/>
     </row>
     <row r="337" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A337" s="156"/>
+      <c r="A337" s="155"/>
       <c r="B337" s="18"/>
       <c r="C337" s="19"/>
       <c r="D337" s="20"/>
@@ -9163,7 +9155,7 @@
       <c r="O337" s="20"/>
     </row>
     <row r="338" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A338" s="156"/>
+      <c r="A338" s="155"/>
       <c r="B338" s="18"/>
       <c r="C338" s="19"/>
       <c r="D338" s="20"/>
@@ -9180,7 +9172,7 @@
       <c r="O338" s="20"/>
     </row>
     <row r="339" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A339" s="156"/>
+      <c r="A339" s="155"/>
       <c r="B339" s="18"/>
       <c r="C339" s="19"/>
       <c r="D339" s="20"/>
@@ -9197,7 +9189,7 @@
       <c r="O339" s="20"/>
     </row>
     <row r="340" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A340" s="156"/>
+      <c r="A340" s="155"/>
       <c r="B340" s="18"/>
       <c r="C340" s="19"/>
       <c r="D340" s="20"/>
@@ -9214,7 +9206,7 @@
       <c r="O340" s="20"/>
     </row>
     <row r="341" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A341" s="156"/>
+      <c r="A341" s="155"/>
       <c r="B341" s="18"/>
       <c r="C341" s="19"/>
       <c r="D341" s="20"/>
@@ -9231,7 +9223,7 @@
       <c r="O341" s="20"/>
     </row>
     <row r="342" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A342" s="156"/>
+      <c r="A342" s="155"/>
       <c r="B342" s="18"/>
       <c r="C342" s="19"/>
       <c r="D342" s="20"/>
@@ -9248,7 +9240,7 @@
       <c r="O342" s="20"/>
     </row>
     <row r="343" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A343" s="156"/>
+      <c r="A343" s="155"/>
       <c r="B343" s="18"/>
       <c r="C343" s="19"/>
       <c r="D343" s="20"/>
@@ -9265,7 +9257,7 @@
       <c r="O343" s="20"/>
     </row>
     <row r="344" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A344" s="156"/>
+      <c r="A344" s="155"/>
       <c r="B344" s="18"/>
       <c r="C344" s="19"/>
       <c r="D344" s="20"/>
@@ -9282,7 +9274,7 @@
       <c r="O344" s="20"/>
     </row>
     <row r="345" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A345" s="156"/>
+      <c r="A345" s="155"/>
       <c r="B345" s="18"/>
       <c r="C345" s="19"/>
       <c r="D345" s="20"/>
@@ -9299,7 +9291,7 @@
       <c r="O345" s="20"/>
     </row>
     <row r="346" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A346" s="156"/>
+      <c r="A346" s="155"/>
       <c r="B346" s="18"/>
       <c r="C346" s="19"/>
       <c r="D346" s="20"/>
@@ -9316,7 +9308,7 @@
       <c r="O346" s="20"/>
     </row>
     <row r="347" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A347" s="156"/>
+      <c r="A347" s="155"/>
       <c r="B347" s="18"/>
       <c r="C347" s="19"/>
       <c r="D347" s="20"/>
@@ -9333,7 +9325,7 @@
       <c r="O347" s="20"/>
     </row>
     <row r="348" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A348" s="156"/>
+      <c r="A348" s="155"/>
       <c r="B348" s="18"/>
       <c r="C348" s="19"/>
       <c r="D348" s="20"/>
@@ -9350,7 +9342,7 @@
       <c r="O348" s="20"/>
     </row>
     <row r="349" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A349" s="156"/>
+      <c r="A349" s="155"/>
       <c r="B349" s="18"/>
       <c r="C349" s="19"/>
       <c r="D349" s="20"/>
@@ -9367,7 +9359,7 @@
       <c r="O349" s="20"/>
     </row>
     <row r="350" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A350" s="156"/>
+      <c r="A350" s="155"/>
       <c r="B350" s="18"/>
       <c r="C350" s="19"/>
       <c r="D350" s="20"/>
@@ -9384,7 +9376,7 @@
       <c r="O350" s="20"/>
     </row>
     <row r="351" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A351" s="156"/>
+      <c r="A351" s="155"/>
       <c r="B351" s="18"/>
       <c r="C351" s="19"/>
       <c r="D351" s="20"/>
@@ -9401,7 +9393,7 @@
       <c r="O351" s="20"/>
     </row>
     <row r="352" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A352" s="156"/>
+      <c r="A352" s="155"/>
       <c r="B352" s="18"/>
       <c r="C352" s="19"/>
       <c r="D352" s="20"/>
@@ -9418,7 +9410,7 @@
       <c r="O352" s="20"/>
     </row>
     <row r="353" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A353" s="156"/>
+      <c r="A353" s="155"/>
       <c r="B353" s="18"/>
       <c r="C353" s="19"/>
       <c r="D353" s="20"/>
@@ -9435,7 +9427,7 @@
       <c r="O353" s="20"/>
     </row>
     <row r="354" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A354" s="156"/>
+      <c r="A354" s="155"/>
       <c r="B354" s="18"/>
       <c r="C354" s="19"/>
       <c r="D354" s="20"/>
@@ -9452,7 +9444,7 @@
       <c r="O354" s="20"/>
     </row>
     <row r="355" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A355" s="156"/>
+      <c r="A355" s="155"/>
       <c r="B355" s="18"/>
       <c r="C355" s="19"/>
       <c r="D355" s="20"/>
@@ -9469,7 +9461,7 @@
       <c r="O355" s="20"/>
     </row>
     <row r="356" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A356" s="156"/>
+      <c r="A356" s="155"/>
       <c r="B356" s="18"/>
       <c r="C356" s="19"/>
       <c r="D356" s="20"/>
@@ -9486,7 +9478,7 @@
       <c r="O356" s="20"/>
     </row>
     <row r="357" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A357" s="156"/>
+      <c r="A357" s="155"/>
       <c r="B357" s="18"/>
       <c r="C357" s="19"/>
       <c r="D357" s="20"/>
@@ -9503,7 +9495,7 @@
       <c r="O357" s="20"/>
     </row>
     <row r="358" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A358" s="156"/>
+      <c r="A358" s="155"/>
       <c r="B358" s="18"/>
       <c r="C358" s="19"/>
       <c r="D358" s="20"/>
@@ -9520,7 +9512,7 @@
       <c r="O358" s="20"/>
     </row>
     <row r="359" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A359" s="156"/>
+      <c r="A359" s="155"/>
       <c r="B359" s="18"/>
       <c r="C359" s="19"/>
       <c r="D359" s="20"/>
@@ -9537,7 +9529,7 @@
       <c r="O359" s="20"/>
     </row>
     <row r="360" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A360" s="156"/>
+      <c r="A360" s="155"/>
       <c r="B360" s="18"/>
       <c r="C360" s="19"/>
       <c r="D360" s="20"/>
@@ -9554,7 +9546,7 @@
       <c r="O360" s="20"/>
     </row>
     <row r="361" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A361" s="156"/>
+      <c r="A361" s="155"/>
       <c r="B361" s="18"/>
       <c r="C361" s="19"/>
       <c r="D361" s="20"/>
@@ -9571,7 +9563,7 @@
       <c r="O361" s="20"/>
     </row>
     <row r="362" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A362" s="156"/>
+      <c r="A362" s="155"/>
       <c r="B362" s="18"/>
       <c r="C362" s="19"/>
       <c r="D362" s="20"/>
@@ -9588,7 +9580,7 @@
       <c r="O362" s="20"/>
     </row>
     <row r="363" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A363" s="156"/>
+      <c r="A363" s="155"/>
       <c r="B363" s="18"/>
       <c r="C363" s="19"/>
       <c r="D363" s="20"/>
@@ -9605,7 +9597,7 @@
       <c r="O363" s="20"/>
     </row>
     <row r="364" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A364" s="156"/>
+      <c r="A364" s="155"/>
       <c r="B364" s="18"/>
       <c r="C364" s="19"/>
       <c r="D364" s="20"/>
@@ -9622,7 +9614,7 @@
       <c r="O364" s="20"/>
     </row>
     <row r="365" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A365" s="156"/>
+      <c r="A365" s="155"/>
       <c r="B365" s="18"/>
       <c r="C365" s="19"/>
       <c r="D365" s="20"/>
@@ -9639,7 +9631,7 @@
       <c r="O365" s="20"/>
     </row>
     <row r="366" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A366" s="156"/>
+      <c r="A366" s="155"/>
       <c r="B366" s="18"/>
       <c r="C366" s="19"/>
       <c r="D366" s="20"/>
@@ -9656,7 +9648,7 @@
       <c r="O366" s="20"/>
     </row>
     <row r="367" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A367" s="156"/>
+      <c r="A367" s="155"/>
       <c r="B367" s="18"/>
       <c r="C367" s="19"/>
       <c r="D367" s="20"/>
@@ -9673,7 +9665,7 @@
       <c r="O367" s="20"/>
     </row>
     <row r="368" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A368" s="156"/>
+      <c r="A368" s="155"/>
       <c r="B368" s="18"/>
       <c r="C368" s="19"/>
       <c r="D368" s="20"/>
@@ -9690,7 +9682,7 @@
       <c r="O368" s="20"/>
     </row>
     <row r="369" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A369" s="156"/>
+      <c r="A369" s="155"/>
       <c r="B369" s="18"/>
       <c r="C369" s="19"/>
       <c r="D369" s="20"/>
@@ -9707,7 +9699,7 @@
       <c r="O369" s="20"/>
     </row>
     <row r="370" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A370" s="156"/>
+      <c r="A370" s="155"/>
       <c r="B370" s="18"/>
       <c r="C370" s="19"/>
       <c r="D370" s="20"/>
@@ -9724,7 +9716,7 @@
       <c r="O370" s="20"/>
     </row>
     <row r="371" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A371" s="156"/>
+      <c r="A371" s="155"/>
       <c r="B371" s="18"/>
       <c r="C371" s="19"/>
       <c r="D371" s="20"/>
@@ -9741,7 +9733,7 @@
       <c r="O371" s="20"/>
     </row>
     <row r="372" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A372" s="156"/>
+      <c r="A372" s="155"/>
       <c r="B372" s="18"/>
       <c r="C372" s="19"/>
       <c r="D372" s="20"/>
@@ -9758,7 +9750,7 @@
       <c r="O372" s="20"/>
     </row>
     <row r="373" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A373" s="156"/>
+      <c r="A373" s="155"/>
       <c r="B373" s="18"/>
       <c r="C373" s="19"/>
       <c r="D373" s="20"/>
@@ -9776,6 +9768,9 @@
     </row>
   </sheetData>
   <autoFilter ref="B2:O373" xr:uid="{D68E069B-CF59-4497-A662-696AA6B25863}"/>
+  <mergeCells count="1">
+    <mergeCell ref="B1:O1"/>
+  </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -9797,25 +9792,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" s="68" customFormat="1" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="189" t="s">
+      <c r="A1" s="184" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="189"/>
-      <c r="C1" s="189"/>
-      <c r="E1" s="189" t="s">
+      <c r="B1" s="184"/>
+      <c r="C1" s="184"/>
+      <c r="E1" s="184" t="s">
         <v>36</v>
       </c>
-      <c r="F1" s="189"/>
-      <c r="G1" s="189"/>
-      <c r="J1" s="190" t="s">
+      <c r="F1" s="184"/>
+      <c r="G1" s="184"/>
+      <c r="J1" s="185" t="s">
         <v>37</v>
       </c>
-      <c r="K1" s="190"/>
-      <c r="L1" s="190"/>
-      <c r="M1" s="190"/>
-      <c r="N1" s="190"/>
-      <c r="O1" s="190"/>
-      <c r="P1" s="190"/>
+      <c r="K1" s="185"/>
+      <c r="L1" s="185"/>
+      <c r="M1" s="185"/>
+      <c r="N1" s="185"/>
+      <c r="O1" s="185"/>
+      <c r="P1" s="185"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="69"/>
@@ -9834,11 +9829,11 @@
       <c r="G2" s="70" t="s">
         <v>41</v>
       </c>
-      <c r="L2" s="191"/>
-      <c r="M2" s="191"/>
-      <c r="N2" s="191"/>
-      <c r="O2" s="191"/>
-      <c r="P2" s="191"/>
+      <c r="L2" s="186"/>
+      <c r="M2" s="186"/>
+      <c r="N2" s="186"/>
+      <c r="O2" s="186"/>
+      <c r="P2" s="186"/>
     </row>
     <row r="3" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="71" t="s">
@@ -9859,7 +9854,7 @@
       <c r="G3" s="74" t="s">
         <v>46</v>
       </c>
-      <c r="I3" s="192" t="s">
+      <c r="I3" s="187" t="s">
         <v>35</v>
       </c>
       <c r="J3" s="75" t="s">
@@ -9904,7 +9899,7 @@
       <c r="G4" s="74" t="s">
         <v>55</v>
       </c>
-      <c r="I4" s="192"/>
+      <c r="I4" s="187"/>
       <c r="J4" s="81" t="s">
         <v>56</v>
       </c>
@@ -9947,7 +9942,7 @@
       <c r="G5" s="74" t="s">
         <v>62</v>
       </c>
-      <c r="I5" s="192"/>
+      <c r="I5" s="187"/>
       <c r="J5" s="84" t="s">
         <v>63</v>
       </c>
@@ -9990,7 +9985,7 @@
       <c r="G6" s="74" t="s">
         <v>68</v>
       </c>
-      <c r="I6" s="192"/>
+      <c r="I6" s="187"/>
       <c r="J6" s="80" t="s">
         <v>69</v>
       </c>
@@ -10033,7 +10028,7 @@
       <c r="G7" s="74" t="s">
         <v>76</v>
       </c>
-      <c r="I7" s="192"/>
+      <c r="I7" s="187"/>
       <c r="J7" s="89" t="s">
         <v>77</v>
       </c>
@@ -10064,11 +10059,11 @@
       <c r="I8" s="67"/>
       <c r="J8" s="94"/>
       <c r="K8" s="94"/>
-      <c r="L8" s="186"/>
-      <c r="M8" s="187"/>
-      <c r="N8" s="187"/>
-      <c r="O8" s="187"/>
-      <c r="P8" s="188"/>
+      <c r="L8" s="181"/>
+      <c r="M8" s="182"/>
+      <c r="N8" s="182"/>
+      <c r="O8" s="182"/>
+      <c r="P8" s="183"/>
     </row>
     <row r="9" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="L9" s="71" t="s">
@@ -10091,19 +10086,19 @@
       <c r="D10" s="58" t="s">
         <v>82</v>
       </c>
-      <c r="L10" s="180" t="s">
+      <c r="L10" s="175" t="s">
         <v>36</v>
       </c>
-      <c r="M10" s="180"/>
-      <c r="N10" s="180"/>
-      <c r="O10" s="180"/>
-      <c r="P10" s="180"/>
+      <c r="M10" s="175"/>
+      <c r="N10" s="175"/>
+      <c r="O10" s="175"/>
+      <c r="P10" s="175"/>
     </row>
     <row r="11" spans="1:18" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="181" t="s">
+      <c r="A11" s="176" t="s">
         <v>83</v>
       </c>
-      <c r="B11" s="182" t="s">
+      <c r="B11" s="177" t="s">
         <v>84</v>
       </c>
       <c r="C11" s="95" t="s">
@@ -10112,15 +10107,15 @@
       <c r="D11" s="96">
         <v>0.25</v>
       </c>
-      <c r="L11" s="180"/>
-      <c r="M11" s="180"/>
-      <c r="N11" s="180"/>
-      <c r="O11" s="180"/>
-      <c r="P11" s="180"/>
+      <c r="L11" s="175"/>
+      <c r="M11" s="175"/>
+      <c r="N11" s="175"/>
+      <c r="O11" s="175"/>
+      <c r="P11" s="175"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A12" s="181"/>
-      <c r="B12" s="183"/>
+      <c r="A12" s="176"/>
+      <c r="B12" s="178"/>
       <c r="C12" s="95" t="s">
         <v>86</v>
       </c>
@@ -10129,8 +10124,8 @@
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A13" s="181"/>
-      <c r="B13" s="183"/>
+      <c r="A13" s="176"/>
+      <c r="B13" s="178"/>
       <c r="C13" s="95" t="s">
         <v>87</v>
       </c>
@@ -10139,8 +10134,8 @@
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A14" s="181"/>
-      <c r="B14" s="179" t="s">
+      <c r="A14" s="176"/>
+      <c r="B14" s="174" t="s">
         <v>88</v>
       </c>
       <c r="C14" s="95" t="s">
@@ -10151,8 +10146,8 @@
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A15" s="181"/>
-      <c r="B15" s="179"/>
+      <c r="A15" s="176"/>
+      <c r="B15" s="174"/>
       <c r="C15" s="95" t="s">
         <v>90</v>
       </c>
@@ -10161,7 +10156,7 @@
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="181" t="s">
+      <c r="A17" s="176" t="s">
         <v>91</v>
       </c>
       <c r="B17" s="95" t="s">
@@ -10169,19 +10164,19 @@
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="181"/>
+      <c r="A18" s="176"/>
       <c r="B18" s="95" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="181"/>
+      <c r="A19" s="176"/>
       <c r="B19" s="95" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="181"/>
+      <c r="A20" s="176"/>
       <c r="B20" s="95" t="s">
         <v>94</v>
       </c>
@@ -10242,10 +10237,10 @@
       <c r="A34" s="101" t="s">
         <v>103</v>
       </c>
-      <c r="B34" s="184" t="s">
+      <c r="B34" s="179" t="s">
         <v>104</v>
       </c>
-      <c r="C34" s="185"/>
+      <c r="C34" s="180"/>
       <c r="D34" s="102" t="s">
         <v>105</v>
       </c>
@@ -10321,7 +10316,7 @@
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="179" t="s">
+      <c r="A40" s="174" t="s">
         <v>115</v>
       </c>
       <c r="B40" s="117" t="s">
@@ -10333,7 +10328,7 @@
       <c r="D40" s="4"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="179"/>
+      <c r="A41" s="174"/>
       <c r="B41" s="118" t="s">
         <v>118</v>
       </c>
@@ -10343,7 +10338,7 @@
       <c r="D41" s="4"/>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="179"/>
+      <c r="A42" s="174"/>
       <c r="B42" s="119" t="s">
         <v>120</v>
       </c>
@@ -10353,7 +10348,7 @@
       <c r="D42" s="4"/>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="179"/>
+      <c r="A43" s="174"/>
       <c r="B43" s="120" t="s">
         <v>122</v>
       </c>
@@ -10363,7 +10358,7 @@
       <c r="D43" s="4"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="179"/>
+      <c r="A44" s="174"/>
       <c r="B44" s="121" t="s">
         <v>124</v>
       </c>
@@ -10509,7 +10504,7 @@
   <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.140625" style="151" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" style="150" customWidth="1"/>
     <col min="2" max="2" width="24.85546875" style="1" customWidth="1"/>
     <col min="3" max="3" width="29.140625" style="1" customWidth="1"/>
     <col min="4" max="4" width="42.140625" style="1" customWidth="1"/>
@@ -10517,25 +10512,25 @@
     <col min="6" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="153" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="152" t="s">
+    <row r="1" spans="1:5" s="152" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="151" t="s">
         <v>142</v>
       </c>
-      <c r="B1" s="152" t="s">
+      <c r="B1" s="151" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="152" t="s">
+      <c r="C1" s="151" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="152" t="s">
+      <c r="D1" s="151" t="s">
         <v>143</v>
       </c>
-      <c r="E1" s="152" t="s">
+      <c r="E1" s="151" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="151" t="s">
+      <c r="A2" s="150" t="s">
         <v>145</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -10552,7 +10547,7 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="151" t="s">
+      <c r="A3" s="150" t="s">
         <v>150</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -10569,7 +10564,7 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="151" t="s">
+      <c r="A4" s="150" t="s">
         <v>154</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -10586,7 +10581,7 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="151" t="s">
+      <c r="A5" s="150" t="s">
         <v>158</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -10603,7 +10598,7 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="151" t="s">
+      <c r="A6" s="150" t="s">
         <v>162</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -10617,7 +10612,7 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="151" t="s">
+      <c r="A7" s="150" t="s">
         <v>165</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -10631,7 +10626,7 @@
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="151" t="s">
+      <c r="A8" s="150" t="s">
         <v>168</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -10645,7 +10640,7 @@
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="151" t="s">
+      <c r="A9" s="150" t="s">
         <v>171</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -10659,7 +10654,7 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="151" t="s">
+      <c r="A10" s="150" t="s">
         <v>174</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -10673,7 +10668,7 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="151" t="s">
+      <c r="A11" s="150" t="s">
         <v>176</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -10687,7 +10682,7 @@
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="151" t="s">
+      <c r="A12" s="150" t="s">
         <v>179</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -10701,7 +10696,7 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="151" t="s">
+      <c r="A13" s="150" t="s">
         <v>181</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -10715,7 +10710,7 @@
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="151" t="s">
+      <c r="A14" s="150" t="s">
         <v>184</v>
       </c>
       <c r="B14" s="1" t="s">
@@ -10729,7 +10724,7 @@
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="151" t="s">
+      <c r="A15" s="150" t="s">
         <v>188</v>
       </c>
       <c r="B15" s="1" t="s">
@@ -10743,7 +10738,7 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="151" t="s">
+      <c r="A16" s="150" t="s">
         <v>190</v>
       </c>
       <c r="B16" s="1" t="s">
@@ -10818,7 +10813,7 @@
       </c>
     </row>
     <row r="25" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="E25" s="154" t="s">
+      <c r="E25" s="153" t="s">
         <v>204</v>
       </c>
     </row>
@@ -11062,13 +11057,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:56" x14ac:dyDescent="0.25">
-      <c r="C1" s="193" t="s">
+      <c r="C1" s="188" t="s">
         <v>245</v>
       </c>
-      <c r="D1" s="194"/>
-      <c r="E1" s="194"/>
-      <c r="F1" s="194"/>
-      <c r="G1" s="194"/>
+      <c r="D1" s="189"/>
+      <c r="E1" s="189"/>
+      <c r="F1" s="189"/>
+      <c r="G1" s="189"/>
       <c r="H1" s="62"/>
     </row>
     <row r="2" spans="1:56" s="25" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -12130,7 +12125,7 @@
       </c>
     </row>
     <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="195" t="s">
+      <c r="A2" s="190" t="s">
         <v>302</v>
       </c>
       <c r="B2" s="131" t="s">
@@ -12153,7 +12148,7 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="196"/>
+      <c r="A3" s="191"/>
       <c r="B3" s="134" t="s">
         <v>304</v>
       </c>
@@ -12174,7 +12169,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="196"/>
+      <c r="A4" s="191"/>
       <c r="B4" s="134" t="s">
         <v>305</v>
       </c>
@@ -12195,7 +12190,7 @@
       </c>
     </row>
     <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="196"/>
+      <c r="A5" s="191"/>
       <c r="B5" s="134" t="s">
         <v>306</v>
       </c>
@@ -12216,7 +12211,7 @@
       </c>
     </row>
     <row r="6" spans="1:7" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="197"/>
+      <c r="A6" s="192"/>
       <c r="B6" s="139" t="s">
         <v>307</v>
       </c>
@@ -12268,10 +12263,10 @@
       <c r="G2" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="I2" s="191" t="s">
+      <c r="I2" s="186" t="s">
         <v>309</v>
       </c>
-      <c r="J2" s="191"/>
+      <c r="J2" s="186"/>
       <c r="K2" t="s">
         <v>310</v>
       </c>
@@ -12658,30 +12653,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="O1" s="200" t="s">
+      <c r="O1" s="195" t="s">
         <v>385</v>
       </c>
-      <c r="P1" s="200"/>
+      <c r="P1" s="195"/>
     </row>
     <row r="2" spans="1:16" ht="204.75" x14ac:dyDescent="0.3">
       <c r="A2" s="16">
         <v>1</v>
       </c>
-      <c r="B2" s="198" t="s">
+      <c r="B2" s="193" t="s">
         <v>386</v>
       </c>
-      <c r="C2" s="198"/>
-      <c r="D2" s="198"/>
-      <c r="E2" s="198"/>
-      <c r="F2" s="198"/>
-      <c r="G2" s="198"/>
-      <c r="H2" s="198"/>
-      <c r="I2" s="198"/>
-      <c r="J2" s="198"/>
-      <c r="K2" s="198"/>
-      <c r="L2" s="198"/>
-      <c r="M2" s="198"/>
-      <c r="N2" s="198"/>
+      <c r="C2" s="193"/>
+      <c r="D2" s="193"/>
+      <c r="E2" s="193"/>
+      <c r="F2" s="193"/>
+      <c r="G2" s="193"/>
+      <c r="H2" s="193"/>
+      <c r="I2" s="193"/>
+      <c r="J2" s="193"/>
+      <c r="K2" s="193"/>
+      <c r="L2" s="193"/>
+      <c r="M2" s="193"/>
+      <c r="N2" s="193"/>
       <c r="O2" s="17" t="s">
         <v>387</v>
       </c>
@@ -12693,21 +12688,21 @@
       <c r="A3" s="16">
         <v>2</v>
       </c>
-      <c r="B3" s="199" t="s">
+      <c r="B3" s="194" t="s">
         <v>389</v>
       </c>
-      <c r="C3" s="199"/>
-      <c r="D3" s="199"/>
-      <c r="E3" s="199"/>
-      <c r="F3" s="199"/>
-      <c r="G3" s="199"/>
-      <c r="H3" s="199"/>
-      <c r="I3" s="199"/>
-      <c r="J3" s="199"/>
-      <c r="K3" s="199"/>
-      <c r="L3" s="199"/>
-      <c r="M3" s="199"/>
-      <c r="N3" s="199"/>
+      <c r="C3" s="194"/>
+      <c r="D3" s="194"/>
+      <c r="E3" s="194"/>
+      <c r="F3" s="194"/>
+      <c r="G3" s="194"/>
+      <c r="H3" s="194"/>
+      <c r="I3" s="194"/>
+      <c r="J3" s="194"/>
+      <c r="K3" s="194"/>
+      <c r="L3" s="194"/>
+      <c r="M3" s="194"/>
+      <c r="N3" s="194"/>
       <c r="O3" s="17" t="s">
         <v>390</v>
       </c>
@@ -12719,21 +12714,21 @@
       <c r="A4" s="16">
         <v>3</v>
       </c>
-      <c r="B4" s="198" t="s">
+      <c r="B4" s="193" t="s">
         <v>392</v>
       </c>
-      <c r="C4" s="198"/>
-      <c r="D4" s="198"/>
-      <c r="E4" s="198"/>
-      <c r="F4" s="198"/>
-      <c r="G4" s="198"/>
-      <c r="H4" s="198"/>
-      <c r="I4" s="198"/>
-      <c r="J4" s="198"/>
-      <c r="K4" s="198"/>
-      <c r="L4" s="198"/>
-      <c r="M4" s="198"/>
-      <c r="N4" s="198"/>
+      <c r="C4" s="193"/>
+      <c r="D4" s="193"/>
+      <c r="E4" s="193"/>
+      <c r="F4" s="193"/>
+      <c r="G4" s="193"/>
+      <c r="H4" s="193"/>
+      <c r="I4" s="193"/>
+      <c r="J4" s="193"/>
+      <c r="K4" s="193"/>
+      <c r="L4" s="193"/>
+      <c r="M4" s="193"/>
+      <c r="N4" s="193"/>
       <c r="O4" s="17" t="s">
         <v>393</v>
       </c>
